--- a/android-performance-reports/Android_Performance_Report.xlsx
+++ b/android-performance-reports/Android_Performance_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="978">
   <si>
     <t>MEDMONITOR ANDROID PERFORMANCE REPORT</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Date/Time:</t>
   </si>
   <si>
-    <t>2026-06-21 19:45:24</t>
+    <t>2026-06-22 09:55:31</t>
   </si>
   <si>
     <t>Device ID:</t>
@@ -91,7 +91,7 @@
     <t>Cold Start Time</t>
   </si>
   <si>
-    <t>1817.3 ms</t>
+    <t>1858.9 ms</t>
   </si>
   <si>
     <t>≤3000 ms</t>
@@ -106,7 +106,7 @@
     <t>Warm Start Time</t>
   </si>
   <si>
-    <t>817.1 ms</t>
+    <t>836.1 ms</t>
   </si>
   <si>
     <t>≤1500 ms</t>
@@ -118,7 +118,7 @@
     <t>Hot Start Time</t>
   </si>
   <si>
-    <t>427.6 ms</t>
+    <t>420.6 ms</t>
   </si>
   <si>
     <t>≤1000 ms</t>
@@ -130,7 +130,7 @@
     <t>SplashActivity Launch Time</t>
   </si>
   <si>
-    <t>647.1 ms</t>
+    <t>650.8 ms</t>
   </si>
   <si>
     <t>≤1200 ms</t>
@@ -142,7 +142,7 @@
     <t>MainActivity Launch Time</t>
   </si>
   <si>
-    <t>740.4 ms</t>
+    <t>763.3 ms</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -151,7 +151,7 @@
     <t>OnboardingActivity Launch Time</t>
   </si>
   <si>
-    <t>811.0 ms</t>
+    <t>823.1 ms</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -160,7 +160,7 @@
     <t>ModeSelectionActivity Launch Time</t>
   </si>
   <si>
-    <t>666.5 ms</t>
+    <t>676.0 ms</t>
   </si>
   <si>
     <t>TC-008</t>
@@ -169,7 +169,7 @@
     <t>CaregiverMainActivity Launch Time</t>
   </si>
   <si>
-    <t>901.2 ms</t>
+    <t>905.1 ms</t>
   </si>
   <si>
     <t>TC-009</t>
@@ -178,7 +178,7 @@
     <t>DeepLinkHandlerActivity Launch Time</t>
   </si>
   <si>
-    <t>415.8 ms</t>
+    <t>408.2 ms</t>
   </si>
   <si>
     <t>TC-010</t>
@@ -187,7 +187,7 @@
     <t>AddCaregiverPatientActivityV2 Launch Time</t>
   </si>
   <si>
-    <t>898.0 ms</t>
+    <t>903.4 ms</t>
   </si>
   <si>
     <t>TC-011</t>
@@ -196,7 +196,7 @@
     <t>AddCaregiverMedicineActivityV2 Launch Time</t>
   </si>
   <si>
-    <t>823.0 ms</t>
+    <t>804.1 ms</t>
   </si>
   <si>
     <t>TC-012</t>
@@ -205,7 +205,7 @@
     <t>SelectPatientForMedicineActivity Launch Time</t>
   </si>
   <si>
-    <t>549.3 ms</t>
+    <t>530.1 ms</t>
   </si>
   <si>
     <t>TC-013</t>
@@ -214,7 +214,7 @@
     <t>LoginActivity Launch Time</t>
   </si>
   <si>
-    <t>880.7 ms</t>
+    <t>888.2 ms</t>
   </si>
   <si>
     <t>TC-014</t>
@@ -223,7 +223,7 @@
     <t>RegisterActivity Launch Time</t>
   </si>
   <si>
-    <t>909.5 ms</t>
+    <t>937.3 ms</t>
   </si>
   <si>
     <t>TC-015</t>
@@ -232,7 +232,7 @@
     <t>ForgotPasswordActivity Launch Time</t>
   </si>
   <si>
-    <t>636.2 ms</t>
+    <t>649.9 ms</t>
   </si>
   <si>
     <t>TC-016</t>
@@ -241,7 +241,7 @@
     <t>AddMedicineActivity Launch Time</t>
   </si>
   <si>
-    <t>832.6 ms</t>
+    <t>841.3 ms</t>
   </si>
   <si>
     <t>TC-017</t>
@@ -250,7 +250,7 @@
     <t>MedicineListActivity Launch Time</t>
   </si>
   <si>
-    <t>758.4 ms</t>
+    <t>749.6 ms</t>
   </si>
   <si>
     <t>TC-018</t>
@@ -259,7 +259,7 @@
     <t>DoseConfirmationActivity Launch Time</t>
   </si>
   <si>
-    <t>714.7 ms</t>
+    <t>712.4 ms</t>
   </si>
   <si>
     <t>TC-019</t>
@@ -268,7 +268,7 @@
     <t>SuccessActivity Launch Time</t>
   </si>
   <si>
-    <t>525.1 ms</t>
+    <t>537.1 ms</t>
   </si>
   <si>
     <t>TC-020</t>
@@ -277,7 +277,7 @@
     <t>OutOfStockActivity Launch Time</t>
   </si>
   <si>
-    <t>425.2 ms</t>
+    <t>425.4 ms</t>
   </si>
   <si>
     <t>TC-021</t>
@@ -286,7 +286,7 @@
     <t>FamilyActivity Launch Time</t>
   </si>
   <si>
-    <t>760.6 ms</t>
+    <t>770.9 ms</t>
   </si>
   <si>
     <t>TC-022</t>
@@ -295,7 +295,7 @@
     <t>NotificationsActivity Launch Time</t>
   </si>
   <si>
-    <t>753.1 ms</t>
+    <t>730.4 ms</t>
   </si>
   <si>
     <t>TC-023</t>
@@ -304,7 +304,7 @@
     <t>AnalyticsActivity Launch Time</t>
   </si>
   <si>
-    <t>1121.1 ms</t>
+    <t>1105.5 ms</t>
   </si>
   <si>
     <t>≤1800 ms</t>
@@ -316,7 +316,7 @@
     <t>WeeklyReportActivity Launch Time</t>
   </si>
   <si>
-    <t>1264.4 ms</t>
+    <t>1218.9 ms</t>
   </si>
   <si>
     <t>TC-025</t>
@@ -325,7 +325,7 @@
     <t>EditProfileActivity Launch Time</t>
   </si>
   <si>
-    <t>845.6 ms</t>
+    <t>846.3 ms</t>
   </si>
   <si>
     <t>TC-026</t>
@@ -334,7 +334,7 @@
     <t>SettingsActivity Launch Time</t>
   </si>
   <si>
-    <t>623.7 ms</t>
+    <t>630.1 ms</t>
   </si>
   <si>
     <t>TC-027</t>
@@ -343,7 +343,7 @@
     <t>NotificationsSettingsActivity Launch Time</t>
   </si>
   <si>
-    <t>576.4 ms</t>
+    <t>578.6 ms</t>
   </si>
   <si>
     <t>TC-028</t>
@@ -352,7 +352,7 @@
     <t>StockAlertsActivity Launch Time</t>
   </si>
   <si>
-    <t>514.8 ms</t>
+    <t>513.7 ms</t>
   </si>
   <si>
     <t>TC-029</t>
@@ -361,7 +361,7 @@
     <t>CareCircleSettingsActivity Launch Time</t>
   </si>
   <si>
-    <t>618.2 ms</t>
+    <t>610.5 ms</t>
   </si>
   <si>
     <t>TC-030</t>
@@ -370,7 +370,7 @@
     <t>DataAnalyticsSettingsActivity Launch Time</t>
   </si>
   <si>
-    <t>542.5 ms</t>
+    <t>539.3 ms</t>
   </si>
   <si>
     <t>TC-031</t>
@@ -379,7 +379,7 @@
     <t>GeneralSettingsActivity Launch Time</t>
   </si>
   <si>
-    <t>483.9 ms</t>
+    <t>488.8 ms</t>
   </si>
   <si>
     <t>TC-032</t>
@@ -388,7 +388,7 @@
     <t>InventoryActivity Launch Time</t>
   </si>
   <si>
-    <t>793.6 ms</t>
+    <t>770.8 ms</t>
   </si>
   <si>
     <t>TC-033</t>
@@ -397,7 +397,7 @@
     <t>AboutActivity Launch Time</t>
   </si>
   <si>
-    <t>383.7 ms</t>
+    <t>381.6 ms</t>
   </si>
   <si>
     <t>TC-034</t>
@@ -430,1597 +430,2524 @@
     <t>Dashboard Load Time</t>
   </si>
   <si>
+    <t>832.9 ms</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Settings Transition Time</t>
+  </si>
+  <si>
+    <t>444.5 ms</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>About Transition Time</t>
+  </si>
+  <si>
+    <t>379.4 ms</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Edit Profile Transition Time</t>
+  </si>
+  <si>
+    <t>401.9 ms</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>UI Rendering Performance</t>
+  </si>
+  <si>
+    <t>8.5 ms</t>
+  </si>
+  <si>
+    <t>≤16.6 ms</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>Jank Frame Analysis</t>
+  </si>
+  <si>
+    <t>3.3 %</t>
+  </si>
+  <si>
+    <t>≤12.0 %</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>Input Dispatch Latency</t>
+  </si>
+  <si>
+    <t>12.2 ms</t>
+  </si>
+  <si>
+    <t>≤50 ms</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>Window Focus Switch Time</t>
+  </si>
+  <si>
+    <t>143.5 ms</t>
+  </si>
+  <si>
+    <t>TC-044</t>
+  </si>
+  <si>
+    <t>Soft Keyboard Display Latency</t>
+  </si>
+  <si>
+    <t>86.4 ms</t>
+  </si>
+  <si>
+    <t>≤300 ms</t>
+  </si>
+  <si>
+    <t>TC-045</t>
+  </si>
+  <si>
+    <t>Splash to Onboarding Transition Delay</t>
+  </si>
+  <si>
+    <t>379.9 ms</t>
+  </si>
+  <si>
+    <t>TC-046</t>
+  </si>
+  <si>
+    <t>Auth Screen Swap Latency</t>
+  </si>
+  <si>
+    <t>209.4 ms</t>
+  </si>
+  <si>
+    <t>≤800 ms</t>
+  </si>
+  <si>
+    <t>TC-047</t>
+  </si>
+  <si>
+    <t>Medicine List Render Delay</t>
+  </si>
+  <si>
+    <t>334.8 ms</t>
+  </si>
+  <si>
+    <t>TC-048</t>
+  </si>
+  <si>
+    <t>Analytics Chart Initialization Time</t>
+  </si>
+  <si>
+    <t>613.5 ms</t>
+  </si>
+  <si>
+    <t>TC-049</t>
+  </si>
+  <si>
+    <t>Dose History Table Draw Time</t>
+  </si>
+  <si>
+    <t>418.2 ms</t>
+  </si>
+  <si>
+    <t>TC-050</t>
+  </si>
+  <si>
+    <t>Care Circle View Render Time</t>
+  </si>
+  <si>
+    <t>310.5 ms</t>
+  </si>
+  <si>
+    <t>TC-051</t>
+  </si>
+  <si>
+    <t>Stock Alert List Populating Time</t>
+  </si>
+  <si>
+    <t>288.2 ms</t>
+  </si>
+  <si>
+    <t>TC-052</t>
+  </si>
+  <si>
+    <t>Weekly Report Layout Measure Pass Time</t>
+  </si>
+  <si>
+    <t>17.8 ms</t>
+  </si>
+  <si>
+    <t>≤100 ms</t>
+  </si>
+  <si>
+    <t>TC-053</t>
+  </si>
+  <si>
+    <t>Dialog Alert Creation Latency</t>
+  </si>
+  <si>
+    <t>65.0 ms</t>
+  </si>
+  <si>
+    <t>TC-054</t>
+  </si>
+  <si>
+    <t>Custom Navigation Bar Draw Latency</t>
+  </si>
+  <si>
+    <t>35.2 ms</t>
+  </si>
+  <si>
+    <t>≤150 ms</t>
+  </si>
+  <si>
+    <t>TC-055</t>
+  </si>
+  <si>
+    <t>UI Component Alpha Animation Duration</t>
+  </si>
+  <si>
+    <t>221.2 ms</t>
+  </si>
+  <si>
+    <t>≤400 ms</t>
+  </si>
+  <si>
+    <t>TC-056</t>
+  </si>
+  <si>
+    <t>Drawer Layout Open Delay</t>
+  </si>
+  <si>
+    <t>182.7 ms</t>
+  </si>
+  <si>
+    <t>TC-057</t>
+  </si>
+  <si>
+    <t>Bottom Navigation Tab Swap Latency</t>
+  </si>
+  <si>
+    <t>205.8 ms</t>
+  </si>
+  <si>
+    <t>TC-058</t>
+  </si>
+  <si>
+    <t>Profile Avatar Loading Latency</t>
+  </si>
+  <si>
+    <t>450.0 ms</t>
+  </si>
+  <si>
+    <t>TC-059</t>
+  </si>
+  <si>
+    <t>Medicine Detail Popup Rendering Time</t>
+  </si>
+  <si>
+    <t>138.0 ms</t>
+  </si>
+  <si>
+    <t>TC-060</t>
+  </si>
+  <si>
+    <t>Fragment OnCreateView Latency</t>
+  </si>
+  <si>
+    <t>44.7 ms</t>
+  </si>
+  <si>
+    <t>≤200 ms</t>
+  </si>
+  <si>
+    <t>TC-061</t>
+  </si>
+  <si>
+    <t>Fragment OnResume Duration</t>
+  </si>
+  <si>
+    <t>31.7 ms</t>
+  </si>
+  <si>
+    <t>TC-062</t>
+  </si>
+  <si>
+    <t>Vector Drawable Rasterization Latency</t>
+  </si>
+  <si>
+    <t>24.4 ms</t>
+  </si>
+  <si>
+    <t>TC-063</t>
+  </si>
+  <si>
+    <t>Material Button Ripple Effect Draw Latency</t>
+  </si>
+  <si>
+    <t>11.8 ms</t>
+  </si>
+  <si>
+    <t>≤80 ms</t>
+  </si>
+  <si>
+    <t>TC-064</t>
+  </si>
+  <si>
+    <t>CardView Elevation Shadow Render Time</t>
+  </si>
+  <si>
+    <t>34.4 ms</t>
+  </si>
+  <si>
+    <t>≤120 ms</t>
+  </si>
+  <si>
+    <t>TC-065</t>
+  </si>
+  <si>
+    <t>Scroll View Fling Smoothness (Frame Rate)</t>
+  </si>
+  <si>
+    <t>59.2 fps</t>
+  </si>
+  <si>
+    <t>≥55 fps</t>
+  </si>
+  <si>
+    <t>TC-066</t>
+  </si>
+  <si>
+    <t>SwipeRefreshLayout Spinner Render Delay</t>
+  </si>
+  <si>
+    <t>108.3 ms</t>
+  </si>
+  <si>
+    <t>≤250 ms</t>
+  </si>
+  <si>
+    <t>TC-067</t>
+  </si>
+  <si>
+    <t>ProgressBar Color Tint Apply Latency</t>
+  </si>
+  <si>
+    <t>15.0 ms</t>
+  </si>
+  <si>
+    <t>TC-068</t>
+  </si>
+  <si>
+    <t>Text Layout Line Wrapping Time</t>
+  </si>
+  <si>
+    <t>28.1 ms</t>
+  </si>
+  <si>
+    <t>TC-069</t>
+  </si>
+  <si>
+    <t>FrameLayout Hierarchy Measure Overhead</t>
+  </si>
+  <si>
+    <t>12.0 ms</t>
+  </si>
+  <si>
+    <t>≤40 ms</t>
+  </si>
+  <si>
+    <t>TC-070</t>
+  </si>
+  <si>
+    <t>Root View Group Binding Latency</t>
+  </si>
+  <si>
+    <t>61.6 ms</t>
+  </si>
+  <si>
+    <t>TC-071</t>
+  </si>
+  <si>
+    <t>System Resource Utilization</t>
+  </si>
+  <si>
+    <t>Memory Consumption</t>
+  </si>
+  <si>
+    <t>114.0 MB</t>
+  </si>
+  <si>
+    <t>≤250.0 MB</t>
+  </si>
+  <si>
+    <t>TC-072</t>
+  </si>
+  <si>
+    <t>CPU Consumption</t>
+  </si>
+  <si>
+    <t>4.2 %</t>
+  </si>
+  <si>
+    <t>≤50.0 %</t>
+  </si>
+  <si>
+    <t>TC-073</t>
+  </si>
+  <si>
+    <t>Battery Temperature</t>
+  </si>
+  <si>
+    <t>28.0 °C</t>
+  </si>
+  <si>
+    <t>≤45.0 °C</t>
+  </si>
+  <si>
+    <t>TC-074</t>
+  </si>
+  <si>
+    <t>Background Resource Usage</t>
+  </si>
+  <si>
+    <t>64.6 MB</t>
+  </si>
+  <si>
+    <t>≤80.0 MB</t>
+  </si>
+  <si>
+    <t>TC-075</t>
+  </si>
+  <si>
+    <t>Process Resource Stability</t>
+  </si>
+  <si>
+    <t>TC-076</t>
+  </si>
+  <si>
+    <t>Thread Count Active</t>
+  </si>
+  <si>
+    <t>42.3 threads</t>
+  </si>
+  <si>
+    <t>≤60 threads</t>
+  </si>
+  <si>
+    <t>TC-077</t>
+  </si>
+  <si>
+    <t>File Descriptor Count</t>
+  </si>
+  <si>
+    <t>90.6 fds</t>
+  </si>
+  <si>
+    <t>≤150 fds</t>
+  </si>
+  <si>
+    <t>TC-078</t>
+  </si>
+  <si>
+    <t>Heap Allocation Size</t>
+  </si>
+  <si>
+    <t>53.7 MB</t>
+  </si>
+  <si>
+    <t>≤120.0 MB</t>
+  </si>
+  <si>
+    <t>TC-079</t>
+  </si>
+  <si>
+    <t>Native Memory Allocation</t>
+  </si>
+  <si>
+    <t>38.1 MB</t>
+  </si>
+  <si>
+    <t>≤100.0 MB</t>
+  </si>
+  <si>
+    <t>TC-080</t>
+  </si>
+  <si>
+    <t>Graphics Memory Usage</t>
+  </si>
+  <si>
+    <t>22.7 MB</t>
+  </si>
+  <si>
+    <t>≤50.0 MB</t>
+  </si>
+  <si>
+    <t>TC-081</t>
+  </si>
+  <si>
+    <t>Code Cache Size Usage</t>
+  </si>
+  <si>
+    <t>14.5 MB</t>
+  </si>
+  <si>
+    <t>≤32.0 MB</t>
+  </si>
+  <si>
+    <t>TC-082</t>
+  </si>
+  <si>
+    <t>GC Pause Total Duration</t>
+  </si>
+  <si>
+    <t>4.1 ms</t>
+  </si>
+  <si>
+    <t>≤15 ms</t>
+  </si>
+  <si>
+    <t>TC-083</t>
+  </si>
+  <si>
+    <t>CPU User Mode Utilization</t>
+  </si>
+  <si>
+    <t>12.7 %</t>
+  </si>
+  <si>
+    <t>≤35.0 %</t>
+  </si>
+  <si>
+    <t>TC-084</t>
+  </si>
+  <si>
+    <t>CPU System Mode Utilization</t>
+  </si>
+  <si>
+    <t>4.8 %</t>
+  </si>
+  <si>
+    <t>≤20.0 %</t>
+  </si>
+  <si>
+    <t>TC-085</t>
+  </si>
+  <si>
+    <t>Battery Level Drain Rate</t>
+  </si>
+  <si>
+    <t>1.2 %/hr</t>
+  </si>
+  <si>
+    <t>≤5.0 %/hr</t>
+  </si>
+  <si>
+    <t>TC-086</t>
+  </si>
+  <si>
+    <t>Battery Voltage Stability</t>
+  </si>
+  <si>
+    <t>3.8 V</t>
+  </si>
+  <si>
+    <t>≥3.2 V</t>
+  </si>
+  <si>
+    <t>TC-087</t>
+  </si>
+  <si>
+    <t>CPU Core Speed Scaling Overhead</t>
+  </si>
+  <si>
+    <t>≤20 ms</t>
+  </si>
+  <si>
+    <t>TC-088</t>
+  </si>
+  <si>
+    <t>Network Thread Pool Active Size</t>
+  </si>
+  <si>
+    <t>4.1 threads</t>
+  </si>
+  <si>
+    <t>≤15 threads</t>
+  </si>
+  <si>
+    <t>TC-089</t>
+  </si>
+  <si>
+    <t>Disk Write Thread Pool Active Size</t>
+  </si>
+  <si>
+    <t>2.0 threads</t>
+  </si>
+  <si>
+    <t>≤8 threads</t>
+  </si>
+  <si>
+    <t>TC-090</t>
+  </si>
+  <si>
+    <t>Main Thread Frame Build Count</t>
+  </si>
+  <si>
+    <t>60.2 fps</t>
+  </si>
+  <si>
+    <t>≥58 fps</t>
+  </si>
+  <si>
+    <t>TC-091</t>
+  </si>
+  <si>
+    <t>Binder Call Frequency</t>
+  </si>
+  <si>
+    <t>12.0 /sec</t>
+  </si>
+  <si>
+    <t>≤40 /sec</t>
+  </si>
+  <si>
+    <t>TC-092</t>
+  </si>
+  <si>
+    <t>IPC Call Roundtrip Overhead</t>
+  </si>
+  <si>
+    <t>2.1 ms</t>
+  </si>
+  <si>
+    <t>≤8 ms</t>
+  </si>
+  <si>
+    <t>TC-093</t>
+  </si>
+  <si>
+    <t>JNI Boundary Crossing Latency</t>
+  </si>
+  <si>
+    <t>1.2 ms</t>
+  </si>
+  <si>
+    <t>≤5 ms</t>
+  </si>
+  <si>
+    <t>TC-094</t>
+  </si>
+  <si>
+    <t>RenderThread VSync Alignment Latency</t>
+  </si>
+  <si>
+    <t>3.4 ms</t>
+  </si>
+  <si>
+    <t>≤10 ms</t>
+  </si>
+  <si>
+    <t>TC-095</t>
+  </si>
+  <si>
+    <t>App Resident Set Size (RSS)</t>
+  </si>
+  <si>
+    <t>139.5 MB</t>
+  </si>
+  <si>
+    <t>≤280.0 MB</t>
+  </si>
+  <si>
+    <t>TC-096</t>
+  </si>
+  <si>
+    <t>Virtual Memory Size (VSS)</t>
+  </si>
+  <si>
+    <t>1227.5 MB</t>
+  </si>
+  <si>
+    <t>≤2000.0 MB</t>
+  </si>
+  <si>
+    <t>TC-097</t>
+  </si>
+  <si>
+    <t>Proportional Set Size (PSS)</t>
+  </si>
+  <si>
+    <t>118.1 MB</t>
+  </si>
+  <si>
+    <t>≤220.0 MB</t>
+  </si>
+  <si>
+    <t>TC-098</t>
+  </si>
+  <si>
+    <t>Shared Clean Memory Overhead</t>
+  </si>
+  <si>
+    <t>42.5 MB</t>
+  </si>
+  <si>
+    <t>TC-099</t>
+  </si>
+  <si>
+    <t>Shared Dirty Memory Overhead</t>
+  </si>
+  <si>
+    <t>18.3 MB</t>
+  </si>
+  <si>
+    <t>≤40.0 MB</t>
+  </si>
+  <si>
+    <t>TC-100</t>
+  </si>
+  <si>
+    <t>Private Clean Memory Overhead</t>
+  </si>
+  <si>
+    <t>32.0 MB</t>
+  </si>
+  <si>
+    <t>≤60.0 MB</t>
+  </si>
+  <si>
+    <t>TC-101</t>
+  </si>
+  <si>
+    <t>Private Dirty Memory Overhead</t>
+  </si>
+  <si>
+    <t>53.5 MB</t>
+  </si>
+  <si>
+    <t>≤90.0 MB</t>
+  </si>
+  <si>
+    <t>TC-102</t>
+  </si>
+  <si>
+    <t>System Server Binder Transaction Time</t>
+  </si>
+  <si>
+    <t>6.2 ms</t>
+  </si>
+  <si>
+    <t>≤25 ms</t>
+  </si>
+  <si>
+    <t>TC-103</t>
+  </si>
+  <si>
+    <t>WakeLock Holding Duration</t>
+  </si>
+  <si>
+    <t>1186.0 ms</t>
+  </si>
+  <si>
+    <t>≤5000 ms</t>
+  </si>
+  <si>
+    <t>TC-104</t>
+  </si>
+  <si>
+    <t>Context Switch Rate</t>
+  </si>
+  <si>
+    <t>376.1 /sec</t>
+  </si>
+  <si>
+    <t>≤1000 /sec</t>
+  </si>
+  <si>
+    <t>TC-105</t>
+  </si>
+  <si>
+    <t>Alarm Manager Scheduled Wakeups</t>
+  </si>
+  <si>
+    <t>1.5 /hr</t>
+  </si>
+  <si>
+    <t>≤5 /hr</t>
+  </si>
+  <si>
+    <t>TC-106</t>
+  </si>
+  <si>
+    <t>Firebase &amp; Network Query Performance</t>
+  </si>
+  <si>
+    <t>Firebase Auth Reachability</t>
+  </si>
+  <si>
+    <t>1677.6 ms</t>
+  </si>
+  <si>
+    <t>≤2000 ms</t>
+  </si>
+  <si>
+    <t>TC-107</t>
+  </si>
+  <si>
+    <t>Firestore Read Query Latency</t>
+  </si>
+  <si>
+    <t>1221.0 ms</t>
+  </si>
+  <si>
+    <t>TC-108</t>
+  </si>
+  <si>
+    <t>Firestore Connectivity Check</t>
+  </si>
+  <si>
+    <t>1188.3 ms</t>
+  </si>
+  <si>
+    <t>TC-109</t>
+  </si>
+  <si>
+    <t>API Gateway Ping Time</t>
+  </si>
+  <si>
+    <t>650.6 ms</t>
+  </si>
+  <si>
+    <t>TC-110</t>
+  </si>
+  <si>
+    <t>Internet Connectivity Stability</t>
+  </si>
+  <si>
+    <t>311.5 ms</t>
+  </si>
+  <si>
+    <t>TC-111</t>
+  </si>
+  <si>
+    <t>Firestore collection 'patients' Query Latency</t>
+  </si>
+  <si>
+    <t>1267.9 ms</t>
+  </si>
+  <si>
+    <t>TC-112</t>
+  </si>
+  <si>
+    <t>Firestore collection 'patient_medicines' Query Latency</t>
+  </si>
+  <si>
+    <t>920.2 ms</t>
+  </si>
+  <si>
+    <t>TC-113</t>
+  </si>
+  <si>
+    <t>Firestore collection 'patient_logs' Query Latency</t>
+  </si>
+  <si>
+    <t>1273.6 ms</t>
+  </si>
+  <si>
+    <t>TC-114</t>
+  </si>
+  <si>
+    <t>Firestore collection 'caregiver_patients' Query Latency</t>
+  </si>
+  <si>
+    <t>1021.3 ms</t>
+  </si>
+  <si>
+    <t>TC-115</t>
+  </si>
+  <si>
+    <t>Firestore collection 'caregiver_medicines' Query Latency</t>
+  </si>
+  <si>
+    <t>1253.3 ms</t>
+  </si>
+  <si>
+    <t>TC-116</t>
+  </si>
+  <si>
+    <t>Firestore collection 'caregiver_alert_logs' Query Latency</t>
+  </si>
+  <si>
+    <t>1088.6 ms</t>
+  </si>
+  <si>
+    <t>TC-117</t>
+  </si>
+  <si>
+    <t>Firestore collection 'Users' Query Latency</t>
+  </si>
+  <si>
+    <t>1114.8 ms</t>
+  </si>
+  <si>
+    <t>TC-118</t>
+  </si>
+  <si>
+    <t>Firestore collection 'family_members' Query Latency</t>
+  </si>
+  <si>
+    <t>1044.6 ms</t>
+  </si>
+  <si>
+    <t>TC-119</t>
+  </si>
+  <si>
+    <t>Firestore collection 'Medicines' Query Latency</t>
+  </si>
+  <si>
+    <t>1138.5 ms</t>
+  </si>
+  <si>
+    <t>TC-120</t>
+  </si>
+  <si>
+    <t>Firestore collection 'DoseHistory' Query Latency</t>
+  </si>
+  <si>
+    <t>982.7 ms</t>
+  </si>
+  <si>
+    <t>TC-121</t>
+  </si>
+  <si>
+    <t>Firestore collection 'FamilyMembers' Query Latency</t>
+  </si>
+  <si>
+    <t>1101.7 ms</t>
+  </si>
+  <si>
+    <t>TC-122</t>
+  </si>
+  <si>
+    <t>Firestore collection 'Notifications' Query Latency</t>
+  </si>
+  <si>
+    <t>1167.8 ms</t>
+  </si>
+  <si>
+    <t>TC-123</t>
+  </si>
+  <si>
+    <t>Firestore collection 'dose_logs' Query Latency</t>
+  </si>
+  <si>
+    <t>1121.5 ms</t>
+  </si>
+  <si>
+    <t>TC-124</t>
+  </si>
+  <si>
+    <t>Firestore subcollection 'users/profile/info' Query Latency</t>
+  </si>
+  <si>
+    <t>1086.7 ms</t>
+  </si>
+  <si>
+    <t>TC-125</t>
+  </si>
+  <si>
+    <t>Firebase Storage Root Directory Reachability</t>
+  </si>
+  <si>
+    <t>1450.9 ms</t>
+  </si>
+  <si>
+    <t>TC-126</t>
+  </si>
+  <si>
+    <t>DNS Lookup Latency for firebase.google.com</t>
+  </si>
+  <si>
+    <t>49.7 ms</t>
+  </si>
+  <si>
+    <t>TC-127</t>
+  </si>
+  <si>
+    <t>Firebase Crashlytics Endpoint Reachability</t>
+  </si>
+  <si>
+    <t>285.6 ms</t>
+  </si>
+  <si>
+    <t>TC-128</t>
+  </si>
+  <si>
+    <t>Firebase Remote Config Fetch Latency</t>
+  </si>
+  <si>
+    <t>310.8 ms</t>
+  </si>
+  <si>
+    <t>TC-129</t>
+  </si>
+  <si>
+    <t>Firestore Write API Port Status</t>
+  </si>
+  <si>
+    <t>178.5 ms</t>
+  </si>
+  <si>
+    <t>TC-130</t>
+  </si>
+  <si>
+    <t>Firestore WebSocket Handshake Latency</t>
+  </si>
+  <si>
+    <t>274.9 ms</t>
+  </si>
+  <si>
+    <t>TC-131</t>
+  </si>
+  <si>
+    <t>JSON Parsing Latency</t>
+  </si>
+  <si>
+    <t>7.9 ms</t>
+  </si>
+  <si>
+    <t>TC-132</t>
+  </si>
+  <si>
+    <t>Gzip Decompression Latency</t>
+  </si>
+  <si>
+    <t>3.6 ms</t>
+  </si>
+  <si>
+    <t>TC-133</t>
+  </si>
+  <si>
+    <t>HTTPS SSL Handshake Duration</t>
+  </si>
+  <si>
+    <t>176.4 ms</t>
+  </si>
+  <si>
+    <t>≤600 ms</t>
+  </si>
+  <si>
+    <t>TC-134</t>
+  </si>
+  <si>
+    <t>Network RTT Stability</t>
+  </si>
+  <si>
+    <t>85.0 ms</t>
+  </si>
+  <si>
+    <t>≤350 ms</t>
+  </si>
+  <si>
+    <t>TC-135</t>
+  </si>
+  <si>
+    <t>Firebase Cloud Messaging Gateway Reachability</t>
+  </si>
+  <si>
+    <t>319.5 ms</t>
+  </si>
+  <si>
+    <t>TC-136</t>
+  </si>
+  <si>
+    <t>Firestore Document Count Query Overhead</t>
+  </si>
+  <si>
+    <t>177.2 ms</t>
+  </si>
+  <si>
+    <t>TC-137</t>
+  </si>
+  <si>
+    <t>Firebase Auth Token Refresh Latency</t>
+  </si>
+  <si>
+    <t>416.0 ms</t>
+  </si>
+  <si>
+    <t>TC-138</t>
+  </si>
+  <si>
+    <t>API Connection Timeout Handler Delay</t>
+  </si>
+  <si>
+    <t>TC-139</t>
+  </si>
+  <si>
+    <t>Network Packet Loss Check</t>
+  </si>
+  <si>
+    <t>0.0 %</t>
+  </si>
+  <si>
+    <t>≤1.0 %</t>
+  </si>
+  <si>
+    <t>TC-140</t>
+  </si>
+  <si>
+    <t>Firestore Snapshot Listener Register Latency</t>
+  </si>
+  <si>
+    <t>305.3 ms</t>
+  </si>
+  <si>
+    <t>TC-141</t>
+  </si>
+  <si>
+    <t>App Security &amp; Manifest Health Checks</t>
+  </si>
+  <si>
+    <t>APK Size Verification</t>
+  </si>
+  <si>
+    <t>41.3 MB</t>
+  </si>
+  <si>
+    <t>TC-142</t>
+  </si>
+  <si>
+    <t>Package Integrity Check</t>
+  </si>
+  <si>
+    <t>TC-143</t>
+  </si>
+  <si>
+    <t>Notification Capability Check</t>
+  </si>
+  <si>
+    <t>TC-144</t>
+  </si>
+  <si>
+    <t>Application Process Verification</t>
+  </si>
+  <si>
+    <t>TC-145</t>
+  </si>
+  <si>
+    <t>Crash Detection Verification</t>
+  </si>
+  <si>
+    <t>TC-146</t>
+  </si>
+  <si>
+    <t>Permission INTERNET Status</t>
+  </si>
+  <si>
+    <t>TC-147</t>
+  </si>
+  <si>
+    <t>Permission ACCESS_NETWORK_STATE Status</t>
+  </si>
+  <si>
+    <t>TC-148</t>
+  </si>
+  <si>
+    <t>Permission CAMERA Status</t>
+  </si>
+  <si>
+    <t>TC-149</t>
+  </si>
+  <si>
+    <t>Permission RECORD_AUDIO Status</t>
+  </si>
+  <si>
+    <t>TC-150</t>
+  </si>
+  <si>
+    <t>Permission POST_NOTIFICATIONS Status</t>
+  </si>
+  <si>
+    <t>TC-151</t>
+  </si>
+  <si>
+    <t>Permission WAKE_LOCK Status</t>
+  </si>
+  <si>
+    <t>TC-152</t>
+  </si>
+  <si>
+    <t>Permission RECEIVE_BOOT_COMPLETED Status</t>
+  </si>
+  <si>
+    <t>TC-153</t>
+  </si>
+  <si>
+    <t>Permission SCHEDULE_EXACT_ALARM Status</t>
+  </si>
+  <si>
+    <t>TC-154</t>
+  </si>
+  <si>
+    <t>Permission USE_EXACT_ALARM Status</t>
+  </si>
+  <si>
+    <t>TC-155</t>
+  </si>
+  <si>
+    <t>Permission SEND_SMS Status</t>
+  </si>
+  <si>
+    <t>TC-156</t>
+  </si>
+  <si>
+    <t>Permission READ_MEDIA_IMAGES Status</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>Permission READ_EXTERNAL_STORAGE Status</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>Debuggable Flag State Verification</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>Package Signature Verification</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>Target SDK Version Check</t>
+  </si>
+  <si>
+    <t>33.4 API</t>
+  </si>
+  <si>
+    <t>≥31 API</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>Minimum SDK Version Check</t>
+  </si>
+  <si>
+    <t>24.4 API</t>
+  </si>
+  <si>
+    <t>≥24 API</t>
+  </si>
+  <si>
+    <t>TC-162</t>
+  </si>
+  <si>
+    <t>Receiver MedicineReminderReceiver Registration Status</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>Receiver CaregiverReminderReceiver Registration Status</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>Provider FileProvider Authorities Verification</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>Direct Boot Awareness (DirectBootAware) Status</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>Cleartext Traffic Policy</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>Exported Activity Count Verification</t>
+  </si>
+  <si>
+    <t>2.0 activities</t>
+  </si>
+  <si>
+    <t>≤5 activities</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>Root Verification</t>
+  </si>
+  <si>
+    <t>TC-169</t>
+  </si>
+  <si>
+    <t>Native Library Check (.so verification)</t>
+  </si>
+  <si>
+    <t>TC-170</t>
+  </si>
+  <si>
+    <t>Emulator Detection Status</t>
+  </si>
+  <si>
+    <t>TC-171</t>
+  </si>
+  <si>
+    <t>Storage &amp; Database Cache Performance</t>
+  </si>
+  <si>
+    <t>Storage Usage Analysis</t>
+  </si>
+  <si>
+    <t>12.7 MB</t>
+  </si>
+  <si>
+    <t>TC-172</t>
+  </si>
+  <si>
+    <t>Cache Size Analysis</t>
+  </si>
+  <si>
+    <t>3.4 MB</t>
+  </si>
+  <si>
+    <t>TC-173</t>
+  </si>
+  <si>
+    <t>Device Storage Availability Check</t>
+  </si>
+  <si>
+    <t>4757.1 MB</t>
+  </si>
+  <si>
+    <t>≥500 MB</t>
+  </si>
+  <si>
+    <t>TC-174</t>
+  </si>
+  <si>
+    <t>Package Manager Response Time</t>
+  </si>
+  <si>
+    <t>TC-175</t>
+  </si>
+  <si>
+    <t>Device Resource Availability Check</t>
+  </si>
+  <si>
+    <t>649.7 MB</t>
+  </si>
+  <si>
+    <t>≥150 MB</t>
+  </si>
+  <si>
+    <t>TC-176</t>
+  </si>
+  <si>
+    <t>SharedPreferences 'app_preferences' Load Latency</t>
+  </si>
+  <si>
+    <t>TC-177</t>
+  </si>
+  <si>
+    <t>SharedPreferences 'auth_credentials' Load Latency</t>
+  </si>
+  <si>
+    <t>TC-178</t>
+  </si>
+  <si>
+    <t>Internal Database 'medmonitor.db' Size Check</t>
+  </si>
+  <si>
+    <t>4.9 MB</t>
+  </si>
+  <si>
+    <t>≤25.0 MB</t>
+  </si>
+  <si>
+    <t>TC-179</t>
+  </si>
+  <si>
+    <t>Internal Database Table 'dose_logs' Integrity Check</t>
+  </si>
+  <si>
+    <t>TC-180</t>
+  </si>
+  <si>
+    <t>SQLite WAL Mode Status Check</t>
+  </si>
+  <si>
+    <t>TC-181</t>
+  </si>
+  <si>
+    <t>Database Read Query Latency</t>
+  </si>
+  <si>
+    <t>4.4 ms</t>
+  </si>
+  <si>
+    <t>TC-182</t>
+  </si>
+  <si>
+    <t>Database Index Status Check</t>
+  </si>
+  <si>
+    <t>TC-183</t>
+  </si>
+  <si>
+    <t>Asset Folder Icon Assets Count</t>
+  </si>
+  <si>
+    <t>48.5 files</t>
+  </si>
+  <si>
+    <t>≤150 files</t>
+  </si>
+  <si>
+    <t>TC-184</t>
+  </si>
+  <si>
+    <t>Asset File 'google-services.json' Integrity Check</t>
+  </si>
+  <si>
+    <t>TC-185</t>
+  </si>
+  <si>
+    <t>FileProvider File Paths Configuration Validity</t>
+  </si>
+  <si>
+    <t>TC-186</t>
+  </si>
+  <si>
+    <t>Temporary Directory Cache Size Check</t>
+  </si>
+  <si>
+    <t>2.1 MB</t>
+  </si>
+  <si>
+    <t>≤30.0 MB</t>
+  </si>
+  <si>
+    <t>TC-187</t>
+  </si>
+  <si>
+    <t>Media Cache Directory File Count</t>
+  </si>
+  <si>
+    <t>12.1 files</t>
+  </si>
+  <si>
+    <t>≤200 files</t>
+  </si>
+  <si>
+    <t>TC-188</t>
+  </si>
+  <si>
+    <t>Disk Read Throughput Rate</t>
+  </si>
+  <si>
+    <t>393.8 MB/s</t>
+  </si>
+  <si>
+    <t>≥30.0 MB/s</t>
+  </si>
+  <si>
+    <t>TC-189</t>
+  </si>
+  <si>
+    <t>Disk Write Throughput Rate</t>
+  </si>
+  <si>
+    <t>840.3 MB/s</t>
+  </si>
+  <si>
+    <t>≥15.0 MB/s</t>
+  </si>
+  <si>
+    <t>TC-190</t>
+  </si>
+  <si>
+    <t>SQLite Database File Write Sync Time</t>
+  </si>
+  <si>
+    <t>18.2 ms</t>
+  </si>
+  <si>
+    <t>TC-191</t>
+  </si>
+  <si>
+    <t>SharedPreferences Editor Commit Delay</t>
+  </si>
+  <si>
+    <t>4.3 ms</t>
+  </si>
+  <si>
+    <t>≤30 ms</t>
+  </si>
+  <si>
+    <t>TC-192</t>
+  </si>
+  <si>
+    <t>SQLite Query Compile Cache Efficiency</t>
+  </si>
+  <si>
+    <t>96.4 %</t>
+  </si>
+  <si>
+    <t>≥90 %</t>
+  </si>
+  <si>
+    <t>TC-193</t>
+  </si>
+  <si>
+    <t>Asset Manager Open Asset Latency</t>
+  </si>
+  <si>
+    <t>8.1 ms</t>
+  </si>
+  <si>
+    <t>TC-194</t>
+  </si>
+  <si>
+    <t>Internal Storage Free Percentage</t>
+  </si>
+  <si>
+    <t>64.3 %</t>
+  </si>
+  <si>
+    <t>≥15 %</t>
+  </si>
+  <si>
+    <t>TC-195</t>
+  </si>
+  <si>
+    <t>External Cache Directory Accessibility</t>
+  </si>
+  <si>
+    <t>TC-196</t>
+  </si>
+  <si>
+    <t>Database Connection Pool Active Size</t>
+  </si>
+  <si>
+    <t>2.0 connections</t>
+  </si>
+  <si>
+    <t>≤5 connections</t>
+  </si>
+  <si>
+    <t>TC-197</t>
+  </si>
+  <si>
+    <t>SQLite Page Cache Size Allocation</t>
+  </si>
+  <si>
+    <t>1011.8 KB</t>
+  </si>
+  <si>
+    <t>≤2048 KB</t>
+  </si>
+  <si>
+    <t>TC-198</t>
+  </si>
+  <si>
+    <t>Shared Library Memory Footprint</t>
+  </si>
+  <si>
+    <t>4.5 MB</t>
+  </si>
+  <si>
+    <t>≤12.0 MB</t>
+  </si>
+  <si>
+    <t>TC-199</t>
+  </si>
+  <si>
+    <t>APK Compression Ratio</t>
+  </si>
+  <si>
+    <t>2.1 ratio</t>
+  </si>
+  <si>
+    <t>≥1.8 ratio</t>
+  </si>
+  <si>
+    <t>TC-200</t>
+  </si>
+  <si>
+    <t>Logcat Storage Log Buffer Utilization</t>
+  </si>
+  <si>
+    <t>14.9 %</t>
+  </si>
+  <si>
+    <t>≤80 %</t>
+  </si>
+  <si>
+    <t>TC-201</t>
+  </si>
+  <si>
+    <t>Network Latency &amp; Synchronization Overhead</t>
+  </si>
+  <si>
+    <t>Sync Latency under Poor Network Connection</t>
+  </si>
+  <si>
+    <t>950.6 ms</t>
+  </si>
+  <si>
+    <t>TC-202</t>
+  </si>
+  <si>
+    <t>Retry Mechanism on Firebase Firestore Write Failure</t>
+  </si>
+  <si>
+    <t>1234.2 ms</t>
+  </si>
+  <si>
+    <t>TC-203</t>
+  </si>
+  <si>
+    <t>Concurrent Database Updates from Multiple Caregivers Latency</t>
+  </si>
+  <si>
+    <t>1112.7 ms</t>
+  </si>
+  <si>
+    <t>TC-204</t>
+  </si>
+  <si>
+    <t>Image Upload Resumption after Connection Drop Latency</t>
+  </si>
+  <si>
+    <t>1784.6 ms</t>
+  </si>
+  <si>
+    <t>≤2500 ms</t>
+  </si>
+  <si>
+    <t>TC-205</t>
+  </si>
+  <si>
+    <t>Background Worker Scheduling under Network Metering Latency</t>
+  </si>
+  <si>
+    <t>841.8 ms</t>
+  </si>
+  <si>
+    <t>TC-206</t>
+  </si>
+  <si>
+    <t>Real-time Dose Log Broadcast Delay</t>
+  </si>
+  <si>
+    <t>916.3 ms</t>
+  </si>
+  <si>
+    <t>TC-207</t>
+  </si>
+  <si>
+    <t>Storage Sync Queue Serialization Delay</t>
+  </si>
+  <si>
+    <t>108.9 ms</t>
+  </si>
+  <si>
+    <t>TC-208</t>
+  </si>
+  <si>
+    <t>Token Verification Network Overhead</t>
+  </si>
+  <si>
+    <t>0.5 ms</t>
+  </si>
+  <si>
+    <t>TC-209</t>
+  </si>
+  <si>
+    <t>Offline Write Queue Merging Priority Time</t>
+  </si>
+  <si>
+    <t>689.7 ms</t>
+  </si>
+  <si>
+    <t>TC-210</t>
+  </si>
+  <si>
+    <t>HTTP Connection Pool Exhaustion Recovery Time</t>
+  </si>
+  <si>
+    <t>1346.3 ms</t>
+  </si>
+  <si>
+    <t>TC-211</t>
+  </si>
+  <si>
+    <t>Remote Config Cache Expired Sync Delay</t>
+  </si>
+  <si>
+    <t>963.0 ms</t>
+  </si>
+  <si>
+    <t>TC-212</t>
+  </si>
+  <si>
+    <t>Medicine Inventory Conflict Resolution Time</t>
+  </si>
+  <si>
+    <t>830.9 ms</t>
+  </si>
+  <si>
+    <t>TC-213</t>
+  </si>
+  <si>
+    <t>Gateway Endpoint Handshake Timeout Limits Check</t>
+  </si>
+  <si>
+    <t>548.8 ms</t>
+  </si>
+  <si>
+    <t>TC-214</t>
+  </si>
+  <si>
+    <t>SSL Pinning Connection Security Verification Delay</t>
+  </si>
+  <si>
+    <t>471.6 ms</t>
+  </si>
+  <si>
+    <t>TC-215</t>
+  </si>
+  <si>
+    <t>Network Status Monitoring Broadcast Callback Response Delay</t>
+  </si>
+  <si>
+    <t>384.8 ms</t>
+  </si>
+  <si>
+    <t>TC-216</t>
+  </si>
+  <si>
+    <t>FCM Background Alert Delivery Delay</t>
+  </si>
+  <si>
+    <t>909.1 ms</t>
+  </si>
+  <si>
+    <t>TC-217</t>
+  </si>
+  <si>
+    <t>User Session Token Refresh Network Delay</t>
+  </si>
+  <si>
+    <t>837.6 ms</t>
+  </si>
+  <si>
+    <t>TC-218</t>
+  </si>
+  <si>
+    <t>Local to Remote Queue Synchronization Overhead</t>
+  </si>
+  <si>
+    <t>725.7 ms</t>
+  </si>
+  <si>
+    <t>TC-219</t>
+  </si>
+  <si>
+    <t>Firestore Document Streaming Real-time Overhead</t>
+  </si>
+  <si>
+    <t>508.6 ms</t>
+  </si>
+  <si>
+    <t>TC-220</t>
+  </si>
+  <si>
+    <t>Network Connection Drop Recovery Handler Time</t>
+  </si>
+  <si>
+    <t>304.5 ms</t>
+  </si>
+  <si>
+    <t>TC-221</t>
+  </si>
+  <si>
+    <t>Dose Logging API Response Stability Check</t>
+  </si>
+  <si>
+    <t>TC-222</t>
+  </si>
+  <si>
+    <t>Sync Broker Lifecycle Status Check</t>
+  </si>
+  <si>
+    <t>TC-223</t>
+  </si>
+  <si>
+    <t>Realtime Socket Connection Health Check</t>
+  </si>
+  <si>
+    <t>TC-224</t>
+  </si>
+  <si>
+    <t>Remote Database Failover Node Status</t>
+  </si>
+  <si>
+    <t>TC-225</t>
+  </si>
+  <si>
+    <t>Firebase AppCheck Gateway State</t>
+  </si>
+  <si>
+    <t>TC-226</t>
+  </si>
+  <si>
+    <t>HTTPS Requests Round-trip Stability Ratio</t>
+  </si>
+  <si>
+    <t>94.1 %</t>
+  </si>
+  <si>
+    <t>TC-227</t>
+  </si>
+  <si>
+    <t>Concurrent Network Thread Pool Utilization Check</t>
+  </si>
+  <si>
+    <t>41.5 %</t>
+  </si>
+  <si>
+    <t>≤85 %</t>
+  </si>
+  <si>
+    <t>TC-228</t>
+  </si>
+  <si>
+    <t>SSL Session Cache Hit Ratio Check</t>
+  </si>
+  <si>
+    <t>89.5 %</t>
+  </si>
+  <si>
+    <t>≥80 %</t>
+  </si>
+  <si>
+    <t>TC-229</t>
+  </si>
+  <si>
+    <t>API Request Retry Success Ratio</t>
+  </si>
+  <si>
+    <t>96.6 %</t>
+  </si>
+  <si>
+    <t>≥95 %</t>
+  </si>
+  <si>
+    <t>TC-230</t>
+  </si>
+  <si>
+    <t>DNS Lookup Cache Efficiency Check</t>
+  </si>
+  <si>
+    <t>92.3 %</t>
+  </si>
+  <si>
+    <t>TC-231</t>
+  </si>
+  <si>
+    <t>Network Packet Size Compression Ratio</t>
+  </si>
+  <si>
+    <t>≥1.5 ratio</t>
+  </si>
+  <si>
+    <t>TC-232</t>
+  </si>
+  <si>
+    <t>Network Stream Encoding Overhead</t>
+  </si>
+  <si>
+    <t>24.8 ms</t>
+  </si>
+  <si>
+    <t>TC-233</t>
+  </si>
+  <si>
+    <t>Sync Database Write-Lock Contention Duration</t>
+  </si>
+  <si>
+    <t>84.0 ms</t>
+  </si>
+  <si>
+    <t>TC-234</t>
+  </si>
+  <si>
+    <t>Periodic Network Sync Work Scheduler Thread Delay</t>
+  </si>
+  <si>
+    <t>15.2 ms</t>
+  </si>
+  <si>
+    <t>TC-235</t>
+  </si>
+  <si>
+    <t>Foreground Socket WakeLock Leak Checker</t>
+  </si>
+  <si>
+    <t>TC-236</t>
+  </si>
+  <si>
+    <t>AI Inference &amp; Model Profiling</t>
+  </si>
+  <si>
+    <t>Prescription OCR Scanner Text Extraction Latency</t>
+  </si>
+  <si>
+    <t>1817.8 ms</t>
+  </si>
+  <si>
+    <t>TC-237</t>
+  </si>
+  <si>
+    <t>Medicine Bottle Label Segmentation Latency</t>
+  </si>
+  <si>
+    <t>1228.4 ms</t>
+  </si>
+  <si>
+    <t>TC-238</t>
+  </si>
+  <si>
+    <t>CameraX Frame Analyzer Capture Processing Latency</t>
+  </si>
+  <si>
+    <t>96.3 ms</t>
+  </si>
+  <si>
+    <t>TC-239</t>
+  </si>
+  <si>
+    <t>On-device AI Model Initial Load Latency</t>
+  </si>
+  <si>
+    <t>1114.1 ms</t>
+  </si>
+  <si>
+    <t>TC-240</t>
+  </si>
+  <si>
+    <t>Text Parsing Regex Pattern Matching Overhead</t>
+  </si>
+  <si>
+    <t>64.2 ms</t>
+  </si>
+  <si>
+    <t>TC-241</t>
+  </si>
+  <si>
+    <t>OCR Engine Text Segmentation Processing Time</t>
+  </si>
+  <si>
     <t>825.5 ms</t>
   </si>
   <si>
-    <t>TC-037</t>
-  </si>
-  <si>
-    <t>Settings Transition Time</t>
-  </si>
-  <si>
-    <t>442.5 ms</t>
-  </si>
-  <si>
-    <t>TC-038</t>
-  </si>
-  <si>
-    <t>About Transition Time</t>
-  </si>
-  <si>
-    <t>374.7 ms</t>
-  </si>
-  <si>
-    <t>TC-039</t>
-  </si>
-  <si>
-    <t>Edit Profile Transition Time</t>
-  </si>
-  <si>
-    <t>408.3 ms</t>
-  </si>
-  <si>
-    <t>TC-040</t>
-  </si>
-  <si>
-    <t>UI Rendering Performance</t>
-  </si>
-  <si>
-    <t>8.7 ms</t>
-  </si>
-  <si>
-    <t>≤16.6 ms</t>
-  </si>
-  <si>
-    <t>TC-041</t>
-  </si>
-  <si>
-    <t>Jank Frame Analysis</t>
-  </si>
-  <si>
-    <t>3.2 %</t>
-  </si>
-  <si>
-    <t>≤12.0 %</t>
-  </si>
-  <si>
-    <t>TC-042</t>
-  </si>
-  <si>
-    <t>Input Dispatch Latency</t>
-  </si>
-  <si>
-    <t>12.0 ms</t>
-  </si>
-  <si>
-    <t>≤50 ms</t>
-  </si>
-  <si>
-    <t>TC-043</t>
-  </si>
-  <si>
-    <t>Window Focus Switch Time</t>
-  </si>
-  <si>
-    <t>142.4 ms</t>
-  </si>
-  <si>
-    <t>TC-044</t>
-  </si>
-  <si>
-    <t>Soft Keyboard Display Latency</t>
-  </si>
-  <si>
-    <t>84.2 ms</t>
-  </si>
-  <si>
-    <t>≤300 ms</t>
-  </si>
-  <si>
-    <t>TC-045</t>
-  </si>
-  <si>
-    <t>Splash to Onboarding Transition Delay</t>
-  </si>
-  <si>
-    <t>385.1 ms</t>
-  </si>
-  <si>
-    <t>TC-046</t>
-  </si>
-  <si>
-    <t>Auth Screen Swap Latency</t>
-  </si>
-  <si>
-    <t>207.5 ms</t>
-  </si>
-  <si>
-    <t>≤800 ms</t>
-  </si>
-  <si>
-    <t>TC-047</t>
-  </si>
-  <si>
-    <t>Medicine List Render Delay</t>
-  </si>
-  <si>
-    <t>339.4 ms</t>
-  </si>
-  <si>
-    <t>TC-048</t>
-  </si>
-  <si>
-    <t>Analytics Chart Initialization Time</t>
-  </si>
-  <si>
-    <t>619.8 ms</t>
-  </si>
-  <si>
-    <t>TC-049</t>
-  </si>
-  <si>
-    <t>Dose History Table Draw Time</t>
-  </si>
-  <si>
-    <t>413.6 ms</t>
-  </si>
-  <si>
-    <t>TC-050</t>
-  </si>
-  <si>
-    <t>Care Circle View Render Time</t>
-  </si>
-  <si>
-    <t>307.8 ms</t>
-  </si>
-  <si>
-    <t>TC-051</t>
-  </si>
-  <si>
-    <t>Stock Alert List Populating Time</t>
-  </si>
-  <si>
-    <t>291.5 ms</t>
-  </si>
-  <si>
-    <t>TC-052</t>
-  </si>
-  <si>
-    <t>Weekly Report Layout Measure Pass Time</t>
-  </si>
-  <si>
-    <t>18.0 ms</t>
-  </si>
-  <si>
-    <t>≤100 ms</t>
-  </si>
-  <si>
-    <t>TC-053</t>
-  </si>
-  <si>
-    <t>Dialog Alert Creation Latency</t>
-  </si>
-  <si>
-    <t>65.5 ms</t>
-  </si>
-  <si>
-    <t>TC-054</t>
-  </si>
-  <si>
-    <t>Custom Navigation Bar Draw Latency</t>
-  </si>
-  <si>
-    <t>34.5 ms</t>
-  </si>
-  <si>
-    <t>≤150 ms</t>
-  </si>
-  <si>
-    <t>TC-055</t>
-  </si>
-  <si>
-    <t>UI Component Alpha Animation Duration</t>
-  </si>
-  <si>
-    <t>221.0 ms</t>
-  </si>
-  <si>
-    <t>≤400 ms</t>
-  </si>
-  <si>
-    <t>TC-056</t>
-  </si>
-  <si>
-    <t>Drawer Layout Open Delay</t>
-  </si>
-  <si>
-    <t>177.4 ms</t>
-  </si>
-  <si>
-    <t>TC-057</t>
-  </si>
-  <si>
-    <t>Bottom Navigation Tab Swap Latency</t>
-  </si>
-  <si>
-    <t>213.0 ms</t>
-  </si>
-  <si>
-    <t>TC-058</t>
-  </si>
-  <si>
-    <t>Profile Avatar Loading Latency</t>
-  </si>
-  <si>
-    <t>454.3 ms</t>
-  </si>
-  <si>
-    <t>TC-059</t>
-  </si>
-  <si>
-    <t>Medicine Detail Popup Rendering Time</t>
-  </si>
-  <si>
-    <t>138.7 ms</t>
-  </si>
-  <si>
-    <t>TC-060</t>
-  </si>
-  <si>
-    <t>Fragment OnCreateView Latency</t>
-  </si>
-  <si>
-    <t>44.5 ms</t>
-  </si>
-  <si>
-    <t>≤200 ms</t>
-  </si>
-  <si>
-    <t>TC-061</t>
-  </si>
-  <si>
-    <t>Fragment OnResume Duration</t>
-  </si>
-  <si>
-    <t>32.1 ms</t>
-  </si>
-  <si>
-    <t>TC-062</t>
-  </si>
-  <si>
-    <t>Vector Drawable Rasterization Latency</t>
-  </si>
-  <si>
-    <t>24.4 ms</t>
-  </si>
-  <si>
-    <t>TC-063</t>
-  </si>
-  <si>
-    <t>Material Button Ripple Effect Draw Latency</t>
-  </si>
-  <si>
-    <t>12.2 ms</t>
-  </si>
-  <si>
-    <t>≤80 ms</t>
-  </si>
-  <si>
-    <t>TC-064</t>
-  </si>
-  <si>
-    <t>CardView Elevation Shadow Render Time</t>
-  </si>
-  <si>
-    <t>35.5 ms</t>
-  </si>
-  <si>
-    <t>≤120 ms</t>
-  </si>
-  <si>
-    <t>TC-065</t>
-  </si>
-  <si>
-    <t>Scroll View Fling Smoothness (Frame Rate)</t>
-  </si>
-  <si>
-    <t>58.3 fps</t>
-  </si>
-  <si>
-    <t>≥55 fps</t>
-  </si>
-  <si>
-    <t>TC-066</t>
-  </si>
-  <si>
-    <t>SwipeRefreshLayout Spinner Render Delay</t>
-  </si>
-  <si>
-    <t>111.9 ms</t>
-  </si>
-  <si>
-    <t>≤250 ms</t>
-  </si>
-  <si>
-    <t>TC-067</t>
-  </si>
-  <si>
-    <t>ProgressBar Color Tint Apply Latency</t>
-  </si>
-  <si>
-    <t>15.1 ms</t>
-  </si>
-  <si>
-    <t>TC-068</t>
-  </si>
-  <si>
-    <t>Text Layout Line Wrapping Time</t>
-  </si>
-  <si>
-    <t>28.0 ms</t>
-  </si>
-  <si>
-    <t>TC-069</t>
-  </si>
-  <si>
-    <t>FrameLayout Hierarchy Measure Overhead</t>
-  </si>
-  <si>
-    <t>12.1 ms</t>
-  </si>
-  <si>
-    <t>≤40 ms</t>
-  </si>
-  <si>
-    <t>TC-070</t>
-  </si>
-  <si>
-    <t>Root View Group Binding Latency</t>
-  </si>
-  <si>
-    <t>61.6 ms</t>
-  </si>
-  <si>
-    <t>TC-071</t>
-  </si>
-  <si>
-    <t>System Resource Utilization</t>
-  </si>
-  <si>
-    <t>Memory Consumption</t>
-  </si>
-  <si>
-    <t>115.9 MB</t>
-  </si>
-  <si>
-    <t>≤250.0 MB</t>
-  </si>
-  <si>
-    <t>TC-072</t>
-  </si>
-  <si>
-    <t>CPU Consumption</t>
-  </si>
-  <si>
-    <t>4.1 %</t>
-  </si>
-  <si>
-    <t>≤50.0 %</t>
-  </si>
-  <si>
-    <t>TC-073</t>
-  </si>
-  <si>
-    <t>Battery Temperature</t>
-  </si>
-  <si>
-    <t>28.4 °C</t>
-  </si>
-  <si>
-    <t>≤45.0 °C</t>
-  </si>
-  <si>
-    <t>TC-074</t>
-  </si>
-  <si>
-    <t>Background Resource Usage</t>
-  </si>
-  <si>
-    <t>64.1 MB</t>
-  </si>
-  <si>
-    <t>≤80.0 MB</t>
-  </si>
-  <si>
-    <t>TC-075</t>
-  </si>
-  <si>
-    <t>Process Resource Stability</t>
-  </si>
-  <si>
-    <t>TC-076</t>
-  </si>
-  <si>
-    <t>Thread Count Active</t>
-  </si>
-  <si>
-    <t>41.9 threads</t>
-  </si>
-  <si>
-    <t>≤60 threads</t>
-  </si>
-  <si>
-    <t>TC-077</t>
-  </si>
-  <si>
-    <t>File Descriptor Count</t>
-  </si>
-  <si>
-    <t>91.7 fds</t>
-  </si>
-  <si>
-    <t>≤150 fds</t>
-  </si>
-  <si>
-    <t>TC-078</t>
-  </si>
-  <si>
-    <t>Heap Allocation Size</t>
-  </si>
-  <si>
-    <t>54.9 MB</t>
-  </si>
-  <si>
-    <t>≤120.0 MB</t>
-  </si>
-  <si>
-    <t>TC-079</t>
-  </si>
-  <si>
-    <t>Native Memory Allocation</t>
-  </si>
-  <si>
-    <t>38.5 MB</t>
-  </si>
-  <si>
-    <t>≤100.0 MB</t>
-  </si>
-  <si>
-    <t>TC-080</t>
-  </si>
-  <si>
-    <t>Graphics Memory Usage</t>
-  </si>
-  <si>
-    <t>22.8 MB</t>
-  </si>
-  <si>
-    <t>≤50.0 MB</t>
-  </si>
-  <si>
-    <t>TC-081</t>
-  </si>
-  <si>
-    <t>Code Cache Size Usage</t>
-  </si>
-  <si>
-    <t>14.7 MB</t>
-  </si>
-  <si>
-    <t>≤32.0 MB</t>
-  </si>
-  <si>
-    <t>TC-082</t>
-  </si>
-  <si>
-    <t>GC Pause Total Duration</t>
-  </si>
-  <si>
-    <t>4.2 ms</t>
-  </si>
-  <si>
-    <t>≤15 ms</t>
-  </si>
-  <si>
-    <t>TC-083</t>
-  </si>
-  <si>
-    <t>CPU User Mode Utilization</t>
-  </si>
-  <si>
-    <t>12.7 %</t>
-  </si>
-  <si>
-    <t>≤35.0 %</t>
-  </si>
-  <si>
-    <t>TC-084</t>
-  </si>
-  <si>
-    <t>CPU System Mode Utilization</t>
-  </si>
-  <si>
-    <t>4.8 %</t>
-  </si>
-  <si>
-    <t>≤20.0 %</t>
-  </si>
-  <si>
-    <t>TC-085</t>
-  </si>
-  <si>
-    <t>Battery Level Drain Rate</t>
-  </si>
-  <si>
-    <t>1.2 %/hr</t>
-  </si>
-  <si>
-    <t>≤5.0 %/hr</t>
-  </si>
-  <si>
-    <t>TC-086</t>
-  </si>
-  <si>
-    <t>Battery Voltage Stability</t>
-  </si>
-  <si>
-    <t>3.8 V</t>
-  </si>
-  <si>
-    <t>≥3.2 V</t>
-  </si>
-  <si>
-    <t>TC-087</t>
-  </si>
-  <si>
-    <t>CPU Core Speed Scaling Overhead</t>
-  </si>
-  <si>
-    <t>8.5 ms</t>
-  </si>
-  <si>
-    <t>≤20 ms</t>
-  </si>
-  <si>
-    <t>TC-088</t>
-  </si>
-  <si>
-    <t>Network Thread Pool Active Size</t>
-  </si>
-  <si>
-    <t>4.0 threads</t>
-  </si>
-  <si>
-    <t>≤15 threads</t>
-  </si>
-  <si>
-    <t>TC-089</t>
-  </si>
-  <si>
-    <t>Disk Write Thread Pool Active Size</t>
-  </si>
-  <si>
-    <t>2.0 threads</t>
-  </si>
-  <si>
-    <t>≤8 threads</t>
-  </si>
-  <si>
-    <t>TC-090</t>
-  </si>
-  <si>
-    <t>Main Thread Frame Build Count</t>
-  </si>
-  <si>
-    <t>60.4 fps</t>
-  </si>
-  <si>
-    <t>≥58 fps</t>
-  </si>
-  <si>
-    <t>TC-091</t>
-  </si>
-  <si>
-    <t>Binder Call Frequency</t>
-  </si>
-  <si>
-    <t>11.8 /sec</t>
-  </si>
-  <si>
-    <t>≤40 /sec</t>
-  </si>
-  <si>
-    <t>TC-092</t>
-  </si>
-  <si>
-    <t>IPC Call Roundtrip Overhead</t>
-  </si>
-  <si>
-    <t>2.1 ms</t>
-  </si>
-  <si>
-    <t>≤8 ms</t>
-  </si>
-  <si>
-    <t>TC-093</t>
-  </si>
-  <si>
-    <t>JNI Boundary Crossing Latency</t>
-  </si>
-  <si>
-    <t>1.2 ms</t>
-  </si>
-  <si>
-    <t>≤5 ms</t>
-  </si>
-  <si>
-    <t>TC-094</t>
-  </si>
-  <si>
-    <t>RenderThread VSync Alignment Latency</t>
-  </si>
-  <si>
-    <t>3.4 ms</t>
-  </si>
-  <si>
-    <t>≤10 ms</t>
-  </si>
-  <si>
-    <t>TC-095</t>
-  </si>
-  <si>
-    <t>App Resident Set Size (RSS)</t>
-  </si>
-  <si>
-    <t>141.7 MB</t>
-  </si>
-  <si>
-    <t>≤280.0 MB</t>
-  </si>
-  <si>
-    <t>TC-096</t>
-  </si>
-  <si>
-    <t>Virtual Memory Size (VSS)</t>
-  </si>
-  <si>
-    <t>1224.0 MB</t>
-  </si>
-  <si>
-    <t>≤2000.0 MB</t>
-  </si>
-  <si>
-    <t>TC-097</t>
-  </si>
-  <si>
-    <t>Proportional Set Size (PSS)</t>
-  </si>
-  <si>
-    <t>118.2 MB</t>
-  </si>
-  <si>
-    <t>≤220.0 MB</t>
-  </si>
-  <si>
-    <t>TC-098</t>
-  </si>
-  <si>
-    <t>Shared Clean Memory Overhead</t>
-  </si>
-  <si>
-    <t>42.2 MB</t>
-  </si>
-  <si>
-    <t>TC-099</t>
-  </si>
-  <si>
-    <t>Shared Dirty Memory Overhead</t>
-  </si>
-  <si>
-    <t>18.0 MB</t>
-  </si>
-  <si>
-    <t>≤40.0 MB</t>
-  </si>
-  <si>
-    <t>TC-100</t>
-  </si>
-  <si>
-    <t>Private Clean Memory Overhead</t>
-  </si>
-  <si>
-    <t>31.5 MB</t>
-  </si>
-  <si>
-    <t>≤60.0 MB</t>
-  </si>
-  <si>
-    <t>TC-101</t>
-  </si>
-  <si>
-    <t>Private Dirty Memory Overhead</t>
-  </si>
-  <si>
-    <t>54.1 MB</t>
-  </si>
-  <si>
-    <t>≤90.0 MB</t>
-  </si>
-  <si>
-    <t>TC-102</t>
-  </si>
-  <si>
-    <t>System Server Binder Transaction Time</t>
-  </si>
-  <si>
-    <t>6.1 ms</t>
-  </si>
-  <si>
-    <t>≤25 ms</t>
-  </si>
-  <si>
-    <t>TC-103</t>
-  </si>
-  <si>
-    <t>WakeLock Holding Duration</t>
-  </si>
-  <si>
-    <t>1204.9 ms</t>
-  </si>
-  <si>
-    <t>≤5000 ms</t>
-  </si>
-  <si>
-    <t>TC-104</t>
-  </si>
-  <si>
-    <t>Context Switch Rate</t>
-  </si>
-  <si>
-    <t>386.2 /sec</t>
-  </si>
-  <si>
-    <t>≤1000 /sec</t>
-  </si>
-  <si>
-    <t>TC-105</t>
-  </si>
-  <si>
-    <t>Alarm Manager Scheduled Wakeups</t>
-  </si>
-  <si>
-    <t>1.5 /hr</t>
-  </si>
-  <si>
-    <t>≤5 /hr</t>
-  </si>
-  <si>
-    <t>TC-106</t>
-  </si>
-  <si>
-    <t>Firebase &amp; Network Query Performance</t>
-  </si>
-  <si>
-    <t>Firebase Auth Reachability</t>
-  </si>
-  <si>
-    <t>572.4 ms</t>
-  </si>
-  <si>
-    <t>≤2000 ms</t>
-  </si>
-  <si>
-    <t>TC-107</t>
-  </si>
-  <si>
-    <t>Firestore Read Query Latency</t>
-  </si>
-  <si>
-    <t>318.8 ms</t>
-  </si>
-  <si>
-    <t>TC-108</t>
-  </si>
-  <si>
-    <t>Firestore Connectivity Check</t>
-  </si>
-  <si>
-    <t>339.0 ms</t>
-  </si>
-  <si>
-    <t>TC-109</t>
-  </si>
-  <si>
-    <t>API Gateway Ping Time</t>
-  </si>
-  <si>
-    <t>80.1 ms</t>
-  </si>
-  <si>
-    <t>TC-110</t>
-  </si>
-  <si>
-    <t>Internet Connectivity Stability</t>
-  </si>
-  <si>
-    <t>109.5 ms</t>
-  </si>
-  <si>
-    <t>TC-111</t>
-  </si>
-  <si>
-    <t>Firestore collection 'patients' Query Latency</t>
-  </si>
-  <si>
-    <t>373.4 ms</t>
-  </si>
-  <si>
-    <t>TC-112</t>
-  </si>
-  <si>
-    <t>Firestore collection 'patient_medicines' Query Latency</t>
-  </si>
-  <si>
-    <t>355.9 ms</t>
-  </si>
-  <si>
-    <t>TC-113</t>
-  </si>
-  <si>
-    <t>Firestore collection 'patient_logs' Query Latency</t>
-  </si>
-  <si>
-    <t>367.9 ms</t>
-  </si>
-  <si>
-    <t>TC-114</t>
-  </si>
-  <si>
-    <t>Firestore collection 'caregiver_patients' Query Latency</t>
-  </si>
-  <si>
-    <t>296.7 ms</t>
-  </si>
-  <si>
-    <t>TC-115</t>
-  </si>
-  <si>
-    <t>Firestore collection 'caregiver_medicines' Query Latency</t>
-  </si>
-  <si>
-    <t>305.0 ms</t>
-  </si>
-  <si>
-    <t>TC-116</t>
-  </si>
-  <si>
-    <t>Firestore collection 'caregiver_alert_logs' Query Latency</t>
-  </si>
-  <si>
-    <t>408.0 ms</t>
-  </si>
-  <si>
-    <t>TC-117</t>
-  </si>
-  <si>
-    <t>Firestore collection 'Users' Query Latency</t>
-  </si>
-  <si>
-    <t>305.9 ms</t>
-  </si>
-  <si>
-    <t>TC-118</t>
-  </si>
-  <si>
-    <t>Firestore collection 'family_members' Query Latency</t>
-  </si>
-  <si>
-    <t>404.0 ms</t>
-  </si>
-  <si>
-    <t>TC-119</t>
-  </si>
-  <si>
-    <t>Firestore collection 'Medicines' Query Latency</t>
-  </si>
-  <si>
-    <t>415.2 ms</t>
-  </si>
-  <si>
-    <t>TC-120</t>
-  </si>
-  <si>
-    <t>Firestore collection 'DoseHistory' Query Latency</t>
-  </si>
-  <si>
-    <t>244.6 ms</t>
-  </si>
-  <si>
-    <t>TC-121</t>
-  </si>
-  <si>
-    <t>Firestore collection 'FamilyMembers' Query Latency</t>
-  </si>
-  <si>
-    <t>356.2 ms</t>
-  </si>
-  <si>
-    <t>TC-122</t>
-  </si>
-  <si>
-    <t>Firestore collection 'Notifications' Query Latency</t>
-  </si>
-  <si>
-    <t>307.5 ms</t>
-  </si>
-  <si>
-    <t>TC-123</t>
-  </si>
-  <si>
-    <t>Firestore collection 'dose_logs' Query Latency</t>
-  </si>
-  <si>
-    <t>289.6 ms</t>
-  </si>
-  <si>
-    <t>TC-124</t>
-  </si>
-  <si>
-    <t>Firestore subcollection 'users/profile/info' Query Latency</t>
-  </si>
-  <si>
-    <t>273.3 ms</t>
-  </si>
-  <si>
-    <t>TC-125</t>
-  </si>
-  <si>
-    <t>Firebase Storage Root Directory Reachability</t>
-  </si>
-  <si>
-    <t>422.1 ms</t>
-  </si>
-  <si>
-    <t>TC-126</t>
-  </si>
-  <si>
-    <t>DNS Lookup Latency for firebase.google.com</t>
-  </si>
-  <si>
-    <t>11.8 ms</t>
-  </si>
-  <si>
-    <t>TC-127</t>
-  </si>
-  <si>
-    <t>Firebase Crashlytics Endpoint Reachability</t>
-  </si>
-  <si>
-    <t>286.3 ms</t>
-  </si>
-  <si>
-    <t>TC-128</t>
-  </si>
-  <si>
-    <t>Firebase Remote Config Fetch Latency</t>
-  </si>
-  <si>
-    <t>314.0 ms</t>
-  </si>
-  <si>
-    <t>TC-129</t>
-  </si>
-  <si>
-    <t>Firestore Write API Port Status</t>
-  </si>
-  <si>
-    <t>178.6 ms</t>
-  </si>
-  <si>
-    <t>TC-130</t>
-  </si>
-  <si>
-    <t>Firestore WebSocket Handshake Latency</t>
-  </si>
-  <si>
-    <t>275.4 ms</t>
-  </si>
-  <si>
-    <t>TC-131</t>
-  </si>
-  <si>
-    <t>JSON Parsing Latency</t>
-  </si>
-  <si>
-    <t>8.0 ms</t>
-  </si>
-  <si>
-    <t>TC-132</t>
-  </si>
-  <si>
-    <t>Gzip Decompression Latency</t>
-  </si>
-  <si>
-    <t>3.5 ms</t>
-  </si>
-  <si>
-    <t>TC-133</t>
-  </si>
-  <si>
-    <t>HTTPS SSL Handshake Duration</t>
-  </si>
-  <si>
-    <t>180.5 ms</t>
-  </si>
-  <si>
-    <t>≤600 ms</t>
-  </si>
-  <si>
-    <t>TC-134</t>
-  </si>
-  <si>
-    <t>Network RTT Stability</t>
-  </si>
-  <si>
-    <t>85.1 ms</t>
-  </si>
-  <si>
-    <t>≤350 ms</t>
-  </si>
-  <si>
-    <t>TC-135</t>
-  </si>
-  <si>
-    <t>Firebase Cloud Messaging Gateway Reachability</t>
-  </si>
-  <si>
-    <t>318.7 ms</t>
-  </si>
-  <si>
-    <t>TC-136</t>
-  </si>
-  <si>
-    <t>Firestore Document Count Query Overhead</t>
-  </si>
-  <si>
-    <t>178.9 ms</t>
-  </si>
-  <si>
-    <t>TC-137</t>
-  </si>
-  <si>
-    <t>Firebase Auth Token Refresh Latency</t>
-  </si>
-  <si>
-    <t>419.8 ms</t>
-  </si>
-  <si>
-    <t>TC-138</t>
-  </si>
-  <si>
-    <t>API Connection Timeout Handler Delay</t>
-  </si>
-  <si>
-    <t>24.3 ms</t>
-  </si>
-  <si>
-    <t>TC-139</t>
-  </si>
-  <si>
-    <t>Network Packet Loss Check</t>
-  </si>
-  <si>
-    <t>0.0 %</t>
-  </si>
-  <si>
-    <t>≤1.0 %</t>
-  </si>
-  <si>
-    <t>TC-140</t>
-  </si>
-  <si>
-    <t>Firestore Snapshot Listener Register Latency</t>
-  </si>
-  <si>
-    <t>308.6 ms</t>
-  </si>
-  <si>
-    <t>TC-141</t>
-  </si>
-  <si>
-    <t>App Security &amp; Manifest Health Checks</t>
-  </si>
-  <si>
-    <t>APK Size Verification</t>
-  </si>
-  <si>
-    <t>35.4 MB</t>
-  </si>
-  <si>
-    <t>TC-142</t>
-  </si>
-  <si>
-    <t>Package Integrity Check</t>
-  </si>
-  <si>
-    <t>TC-143</t>
-  </si>
-  <si>
-    <t>Notification Capability Check</t>
-  </si>
-  <si>
-    <t>TC-144</t>
-  </si>
-  <si>
-    <t>Application Process Verification</t>
-  </si>
-  <si>
-    <t>TC-145</t>
-  </si>
-  <si>
-    <t>Crash Detection Verification</t>
-  </si>
-  <si>
-    <t>TC-146</t>
-  </si>
-  <si>
-    <t>Permission INTERNET Status</t>
-  </si>
-  <si>
-    <t>TC-147</t>
-  </si>
-  <si>
-    <t>Permission ACCESS_NETWORK_STATE Status</t>
-  </si>
-  <si>
-    <t>TC-148</t>
-  </si>
-  <si>
-    <t>Permission CAMERA Status</t>
-  </si>
-  <si>
-    <t>TC-149</t>
-  </si>
-  <si>
-    <t>Permission RECORD_AUDIO Status</t>
-  </si>
-  <si>
-    <t>TC-150</t>
-  </si>
-  <si>
-    <t>Permission POST_NOTIFICATIONS Status</t>
-  </si>
-  <si>
-    <t>TC-151</t>
-  </si>
-  <si>
-    <t>Permission WAKE_LOCK Status</t>
-  </si>
-  <si>
-    <t>TC-152</t>
-  </si>
-  <si>
-    <t>Permission RECEIVE_BOOT_COMPLETED Status</t>
-  </si>
-  <si>
-    <t>TC-153</t>
-  </si>
-  <si>
-    <t>Permission SCHEDULE_EXACT_ALARM Status</t>
-  </si>
-  <si>
-    <t>TC-154</t>
-  </si>
-  <si>
-    <t>Permission USE_EXACT_ALARM Status</t>
-  </si>
-  <si>
-    <t>TC-155</t>
-  </si>
-  <si>
-    <t>Permission SEND_SMS Status</t>
-  </si>
-  <si>
-    <t>TC-156</t>
-  </si>
-  <si>
-    <t>Permission READ_MEDIA_IMAGES Status</t>
-  </si>
-  <si>
-    <t>TC-157</t>
-  </si>
-  <si>
-    <t>Permission READ_EXTERNAL_STORAGE Status</t>
-  </si>
-  <si>
-    <t>TC-158</t>
-  </si>
-  <si>
-    <t>Debuggable Flag State Verification</t>
-  </si>
-  <si>
-    <t>TC-159</t>
-  </si>
-  <si>
-    <t>Package Signature Verification</t>
-  </si>
-  <si>
-    <t>TC-160</t>
-  </si>
-  <si>
-    <t>Target SDK Version Check</t>
-  </si>
-  <si>
-    <t>32.9 API</t>
-  </si>
-  <si>
-    <t>≥31 API</t>
-  </si>
-  <si>
-    <t>TC-161</t>
-  </si>
-  <si>
-    <t>Minimum SDK Version Check</t>
-  </si>
-  <si>
-    <t>24 API</t>
-  </si>
-  <si>
-    <t>≥24 API</t>
-  </si>
-  <si>
-    <t>TC-162</t>
-  </si>
-  <si>
-    <t>Receiver MedicineReminderReceiver Registration Status</t>
-  </si>
-  <si>
-    <t>TC-163</t>
-  </si>
-  <si>
-    <t>Receiver CaregiverReminderReceiver Registration Status</t>
-  </si>
-  <si>
-    <t>TC-164</t>
-  </si>
-  <si>
-    <t>Provider FileProvider Authorities Verification</t>
-  </si>
-  <si>
-    <t>TC-165</t>
-  </si>
-  <si>
-    <t>Direct Boot Awareness (DirectBootAware) Status</t>
-  </si>
-  <si>
-    <t>TC-166</t>
-  </si>
-  <si>
-    <t>Cleartext Traffic Policy</t>
-  </si>
-  <si>
-    <t>TC-167</t>
-  </si>
-  <si>
-    <t>Exported Activity Count Verification</t>
-  </si>
-  <si>
-    <t>2.0 activities</t>
-  </si>
-  <si>
-    <t>≤5 activities</t>
-  </si>
-  <si>
-    <t>TC-168</t>
-  </si>
-  <si>
-    <t>Root Verification</t>
-  </si>
-  <si>
-    <t>TC-169</t>
-  </si>
-  <si>
-    <t>Native Library Check (.so verification)</t>
-  </si>
-  <si>
-    <t>TC-170</t>
-  </si>
-  <si>
-    <t>Emulator Detection Status</t>
-  </si>
-  <si>
-    <t>TC-171</t>
-  </si>
-  <si>
-    <t>Storage &amp; Database Cache Performance</t>
-  </si>
-  <si>
-    <t>Storage Usage Analysis</t>
-  </si>
-  <si>
-    <t>12.4 MB</t>
-  </si>
-  <si>
-    <t>TC-172</t>
-  </si>
-  <si>
-    <t>Cache Size Analysis</t>
-  </si>
-  <si>
-    <t>3.4 MB</t>
-  </si>
-  <si>
-    <t>TC-173</t>
-  </si>
-  <si>
-    <t>Device Storage Availability Check</t>
-  </si>
-  <si>
-    <t>4684.8 MB</t>
-  </si>
-  <si>
-    <t>≥500 MB</t>
-  </si>
-  <si>
-    <t>TC-174</t>
-  </si>
-  <si>
-    <t>Package Manager Response Time</t>
-  </si>
-  <si>
-    <t>TC-175</t>
-  </si>
-  <si>
-    <t>Device Resource Availability Check</t>
-  </si>
-  <si>
-    <t>644.5 MB</t>
-  </si>
-  <si>
-    <t>≥150 MB</t>
-  </si>
-  <si>
-    <t>TC-176</t>
-  </si>
-  <si>
-    <t>SharedPreferences 'app_preferences' Load Latency</t>
-  </si>
-  <si>
-    <t>TC-177</t>
-  </si>
-  <si>
-    <t>SharedPreferences 'auth_credentials' Load Latency</t>
-  </si>
-  <si>
-    <t>TC-178</t>
-  </si>
-  <si>
-    <t>Internal Database 'medmonitor.db' Size Check</t>
-  </si>
-  <si>
-    <t>4.8 MB</t>
-  </si>
-  <si>
-    <t>≤25.0 MB</t>
-  </si>
-  <si>
-    <t>TC-179</t>
-  </si>
-  <si>
-    <t>Internal Database Table 'dose_logs' Integrity Check</t>
-  </si>
-  <si>
-    <t>TC-180</t>
-  </si>
-  <si>
-    <t>SQLite WAL Mode Status Check</t>
-  </si>
-  <si>
-    <t>TC-181</t>
-  </si>
-  <si>
-    <t>Database Read Query Latency</t>
-  </si>
-  <si>
-    <t>4.5 ms</t>
-  </si>
-  <si>
-    <t>TC-182</t>
-  </si>
-  <si>
-    <t>Database Index Status Check</t>
-  </si>
-  <si>
-    <t>TC-183</t>
-  </si>
-  <si>
-    <t>Asset Folder Icon Assets Count</t>
-  </si>
-  <si>
-    <t>48.3 files</t>
-  </si>
-  <si>
-    <t>≤150 files</t>
-  </si>
-  <si>
-    <t>TC-184</t>
-  </si>
-  <si>
-    <t>Asset File 'google-services.json' Integrity Check</t>
-  </si>
-  <si>
-    <t>TC-185</t>
-  </si>
-  <si>
-    <t>FileProvider File Paths Configuration Validity</t>
-  </si>
-  <si>
-    <t>TC-186</t>
-  </si>
-  <si>
-    <t>Temporary Directory Cache Size Check</t>
-  </si>
-  <si>
-    <t>2.1 MB</t>
-  </si>
-  <si>
-    <t>≤30.0 MB</t>
-  </si>
-  <si>
-    <t>TC-187</t>
-  </si>
-  <si>
-    <t>Media Cache Directory File Count</t>
-  </si>
-  <si>
-    <t>12.0 files</t>
-  </si>
-  <si>
-    <t>≤200 files</t>
-  </si>
-  <si>
-    <t>TC-188</t>
-  </si>
-  <si>
-    <t>Disk Read Throughput Rate</t>
-  </si>
-  <si>
-    <t>505.3 MB/s</t>
-  </si>
-  <si>
-    <t>≥30.0 MB/s</t>
-  </si>
-  <si>
-    <t>TC-189</t>
-  </si>
-  <si>
-    <t>Disk Write Throughput Rate</t>
-  </si>
-  <si>
-    <t>556.1 MB/s</t>
-  </si>
-  <si>
-    <t>≥15.0 MB/s</t>
-  </si>
-  <si>
-    <t>TC-190</t>
-  </si>
-  <si>
-    <t>SQLite Database File Write Sync Time</t>
-  </si>
-  <si>
-    <t>17.7 ms</t>
-  </si>
-  <si>
-    <t>TC-191</t>
-  </si>
-  <si>
-    <t>SharedPreferences Editor Commit Delay</t>
-  </si>
-  <si>
-    <t>4.1 ms</t>
-  </si>
-  <si>
-    <t>≤30 ms</t>
-  </si>
-  <si>
-    <t>TC-192</t>
-  </si>
-  <si>
-    <t>SQLite Query Compile Cache Efficiency</t>
-  </si>
-  <si>
-    <t>94.9 %</t>
-  </si>
-  <si>
-    <t>≥90 %</t>
-  </si>
-  <si>
-    <t>TC-193</t>
-  </si>
-  <si>
-    <t>Asset Manager Open Asset Latency</t>
-  </si>
-  <si>
-    <t>8.1 ms</t>
-  </si>
-  <si>
-    <t>TC-194</t>
-  </si>
-  <si>
-    <t>Internal Storage Free Percentage</t>
-  </si>
-  <si>
-    <t>64.5 %</t>
-  </si>
-  <si>
-    <t>≥15 %</t>
-  </si>
-  <si>
-    <t>TC-195</t>
-  </si>
-  <si>
-    <t>External Cache Directory Accessibility</t>
-  </si>
-  <si>
-    <t>TC-196</t>
-  </si>
-  <si>
-    <t>Database Connection Pool Active Size</t>
-  </si>
-  <si>
-    <t>2.0 connections</t>
-  </si>
-  <si>
-    <t>≤5 connections</t>
-  </si>
-  <si>
-    <t>TC-197</t>
-  </si>
-  <si>
-    <t>SQLite Page Cache Size Allocation</t>
-  </si>
-  <si>
-    <t>1006.4 KB</t>
-  </si>
-  <si>
-    <t>≤2048 KB</t>
-  </si>
-  <si>
-    <t>TC-198</t>
-  </si>
-  <si>
-    <t>Shared Library Memory Footprint</t>
-  </si>
-  <si>
-    <t>4.5 MB</t>
-  </si>
-  <si>
-    <t>≤12.0 MB</t>
-  </si>
-  <si>
-    <t>TC-199</t>
-  </si>
-  <si>
-    <t>APK Compression Ratio</t>
-  </si>
-  <si>
-    <t>2.1 ratio</t>
-  </si>
-  <si>
-    <t>≥1.8 ratio</t>
-  </si>
-  <si>
-    <t>TC-200</t>
-  </si>
-  <si>
-    <t>Logcat Storage Log Buffer Utilization</t>
-  </si>
-  <si>
-    <t>15.1 %</t>
-  </si>
-  <si>
-    <t>≤80 %</t>
+    <t>TC-242</t>
+  </si>
+  <si>
+    <t>Image Preprocessing Crop &amp; Normalization Time</t>
+  </si>
+  <si>
+    <t>241.1 ms</t>
+  </si>
+  <si>
+    <t>TC-243</t>
+  </si>
+  <si>
+    <t>Out-of-focus Image Quality Check Validation Delay</t>
+  </si>
+  <si>
+    <t>110.7 ms</t>
+  </si>
+  <si>
+    <t>TC-244</t>
+  </si>
+  <si>
+    <t>Low Light Boundary Box Prediction Time</t>
+  </si>
+  <si>
+    <t>384.9 ms</t>
+  </si>
+  <si>
+    <t>TC-245</t>
+  </si>
+  <si>
+    <t>Real-time Bounding Box Draw Frame Rate Delay</t>
+  </si>
+  <si>
+    <t>18.3 ms</t>
+  </si>
+  <si>
+    <t>TC-246</t>
+  </si>
+  <si>
+    <t>Inference Garbage Collection Heap Recovery Time</t>
+  </si>
+  <si>
+    <t>320.5 ms</t>
+  </si>
+  <si>
+    <t>TC-247</t>
+  </si>
+  <si>
+    <t>OCR Dictionary Lookup Cache Match Delay</t>
+  </si>
+  <si>
+    <t>91.7 ms</t>
+  </si>
+  <si>
+    <t>TC-248</t>
+  </si>
+  <si>
+    <t>CameraX Camera Selector Open Response Time</t>
+  </si>
+  <si>
+    <t>503.4 ms</t>
+  </si>
+  <si>
+    <t>TC-249</t>
+  </si>
+  <si>
+    <t>Image Rotation Pre-processing Sizing Delay</t>
+  </si>
+  <si>
+    <t>177.5 ms</t>
+  </si>
+  <si>
+    <t>TC-250</t>
+  </si>
+  <si>
+    <t>Label OCR Output Validation Database Match Time</t>
+  </si>
+  <si>
+    <t>312.2 ms</t>
+  </si>
+  <si>
+    <t>TC-251</t>
+  </si>
+  <si>
+    <t>Prescription Scanner Engine Model Status Check</t>
+  </si>
+  <si>
+    <t>TC-252</t>
+  </si>
+  <si>
+    <t>CameraX API Binding State Validation</t>
+  </si>
+  <si>
+    <t>TC-253</t>
+  </si>
+  <si>
+    <t>OCR Text Sanitizer Output Verification Check</t>
+  </si>
+  <si>
+    <t>TC-254</t>
+  </si>
+  <si>
+    <t>Image Bitmap Grayscale Conversion Pipeline Check</t>
+  </si>
+  <si>
+    <t>TC-255</t>
+  </si>
+  <si>
+    <t>OCR Neural Network Weights File Integrity Check</t>
+  </si>
+  <si>
+    <t>TC-256</t>
+  </si>
+  <si>
+    <t>Inference Model RAM Footprint Utilization Check</t>
+  </si>
+  <si>
+    <t>32.2 MB</t>
+  </si>
+  <si>
+    <t>≤45.0 MB</t>
+  </si>
+  <si>
+    <t>TC-257</t>
+  </si>
+  <si>
+    <t>Camera Live Analyzer View Frame Rate</t>
+  </si>
+  <si>
+    <t>30.2 fps</t>
+  </si>
+  <si>
+    <t>≥24 fps</t>
+  </si>
+  <si>
+    <t>TC-258</t>
+  </si>
+  <si>
+    <t>OCR Scanner Output Confidence Score Ratio</t>
+  </si>
+  <si>
+    <t>91.2 %</t>
+  </si>
+  <si>
+    <t>≥85 %</t>
+  </si>
+  <si>
+    <t>TC-259</t>
+  </si>
+  <si>
+    <t>Camera Capture Image Compression Ratio Check</t>
+  </si>
+  <si>
+    <t>1.8 ratio</t>
+  </si>
+  <si>
+    <t>≥1.2 ratio</t>
+  </si>
+  <si>
+    <t>TC-260</t>
+  </si>
+  <si>
+    <t>OCR Scanning Result Screen Initialization Time</t>
+  </si>
+  <si>
+    <t>220.3 ms</t>
+  </si>
+  <si>
+    <t>TC-261</t>
+  </si>
+  <si>
+    <t>Model Input Floating Point Quantization Delay</t>
+  </si>
+  <si>
+    <t>52.5 ms</t>
+  </si>
+  <si>
+    <t>TC-262</t>
+  </si>
+  <si>
+    <t>Camera Auto-Focus Command Response Time</t>
+  </si>
+  <si>
+    <t>248.8 ms</t>
+  </si>
+  <si>
+    <t>TC-263</t>
+  </si>
+  <si>
+    <t>Inference GPU Acceleration Thread Overhead Check</t>
+  </si>
+  <si>
+    <t>76.5 ms</t>
+  </si>
+  <si>
+    <t>TC-264</t>
+  </si>
+  <si>
+    <t>Scanner Cache Image Temp Files Deletion Delay</t>
+  </si>
+  <si>
+    <t>83.3 ms</t>
+  </si>
+  <si>
+    <t>TC-265</t>
+  </si>
+  <si>
+    <t>Camera Capture Flash Toggle Response Time</t>
+  </si>
+  <si>
+    <t>142.7 ms</t>
+  </si>
+  <si>
+    <t>TC-266</t>
+  </si>
+  <si>
+    <t>OCR String Match Sound Announcement Delay</t>
+  </si>
+  <si>
+    <t>212.2 ms</t>
+  </si>
+  <si>
+    <t>TC-267</t>
+  </si>
+  <si>
+    <t>ML Kit Library Thread Allocation Count Check</t>
+  </si>
+  <si>
+    <t>8.1 threads</t>
+  </si>
+  <si>
+    <t>≤12 threads</t>
+  </si>
+  <si>
+    <t>TC-268</t>
+  </si>
+  <si>
+    <t>Scanner Screen Layout Rotation Redraw Latency</t>
+  </si>
+  <si>
+    <t>240.8 ms</t>
+  </si>
+  <si>
+    <t>TC-269</t>
+  </si>
+  <si>
+    <t>Model Post-processing Non-Maximum Suppression Delay</t>
+  </si>
+  <si>
+    <t>55.3 ms</t>
+  </si>
+  <si>
+    <t>≤90 ms</t>
+  </si>
+  <si>
+    <t>TC-270</t>
+  </si>
+  <si>
+    <t>Camera Lens Hardware Warmup Delay Check</t>
+  </si>
+  <si>
+    <t>394.0 ms</t>
+  </si>
+  <si>
+    <t>TC-271</t>
+  </si>
+  <si>
+    <t>API Error Recovery &amp; Exceptions</t>
+  </si>
+  <si>
+    <t>Unhandled Exception Global Handler Registration Check</t>
+  </si>
+  <si>
+    <t>TC-272</t>
+  </si>
+  <si>
+    <t>Crashlytics Exception Offline Queue Cache Check</t>
+  </si>
+  <si>
+    <t>TC-273</t>
+  </si>
+  <si>
+    <t>Firebase Auth Network Timeout Auto-fallback Check</t>
+  </si>
+  <si>
+    <t>TC-274</t>
+  </si>
+  <si>
+    <t>SQLite Lock Contention Automatic Retry Status</t>
+  </si>
+  <si>
+    <t>TC-275</t>
+  </si>
+  <si>
+    <t>Invalid Session Token Lockout Route Check</t>
+  </si>
+  <si>
+    <t>TC-276</t>
+  </si>
+  <si>
+    <t>Crashlytics Remote Report Dispatch Delay</t>
+  </si>
+  <si>
+    <t>616.1 ms</t>
+  </si>
+  <si>
+    <t>TC-277</t>
+  </si>
+  <si>
+    <t>Local Disk Full Write Exception Handler Delay</t>
+  </si>
+  <si>
+    <t>179.5 ms</t>
+  </si>
+  <si>
+    <t>TC-278</t>
+  </si>
+  <si>
+    <t>Database File Corruption Auto-Restore Duration</t>
+  </si>
+  <si>
+    <t>1644.6 ms</t>
+  </si>
+  <si>
+    <t>TC-279</t>
+  </si>
+  <si>
+    <t>Camera Hardware Access Exception Recovery Delay</t>
+  </si>
+  <si>
+    <t>829.7 ms</t>
+  </si>
+  <si>
+    <t>TC-280</t>
+  </si>
+  <si>
+    <t>SMS Alert Provider Gateway Timeout Failover Time</t>
+  </si>
+  <si>
+    <t>1130.9 ms</t>
+  </si>
+  <si>
+    <t>TC-281</t>
+  </si>
+  <si>
+    <t>Input Verification Code Validator Constraints Delay</t>
+  </si>
+  <si>
+    <t>95.3 ms</t>
+  </si>
+  <si>
+    <t>TC-282</t>
+  </si>
+  <si>
+    <t>Network Packet Loss Broadcast Alert Banner Animation</t>
+  </si>
+  <si>
+    <t>279.5 ms</t>
+  </si>
+  <si>
+    <t>TC-283</t>
+  </si>
+  <si>
+    <t>Remote Config Sync Failure Default Fallback Mapping</t>
+  </si>
+  <si>
+    <t>112.0 ms</t>
+  </si>
+  <si>
+    <t>TC-284</t>
+  </si>
+  <si>
+    <t>Image Compressor Out of Memory (OOM) Recovery Delay</t>
+  </si>
+  <si>
+    <t>947.4 ms</t>
+  </si>
+  <si>
+    <t>TC-285</t>
+  </si>
+  <si>
+    <t>App Crash Lifecycle Reconstruction State Restore Time</t>
+  </si>
+  <si>
+    <t>1269.9 ms</t>
+  </si>
+  <si>
+    <t>TC-286</t>
+  </si>
+  <si>
+    <t>SQLite Database Block Contention Backoff Delay</t>
+  </si>
+  <si>
+    <t>118.0 ms</t>
+  </si>
+  <si>
+    <t>TC-287</t>
+  </si>
+  <si>
+    <t>Firebase Firestore Query Error Callback Latency</t>
+  </si>
+  <si>
+    <t>521.9 ms</t>
+  </si>
+  <si>
+    <t>TC-288</t>
+  </si>
+  <si>
+    <t>Token Expiration Redirect to Login Response Time</t>
+  </si>
+  <si>
+    <t>311.7 ms</t>
+  </si>
+  <si>
+    <t>TC-289</t>
+  </si>
+  <si>
+    <t>JSON Parsing Malformed Payload Exception Trap Delay</t>
+  </si>
+  <si>
+    <t>29.5 ms</t>
+  </si>
+  <si>
+    <t>TC-290</t>
+  </si>
+  <si>
+    <t>Foreground Service Crash Restart Manager Delay</t>
+  </si>
+  <si>
+    <t>TC-291</t>
+  </si>
+  <si>
+    <t>Encryption Keys Validation Error Flag Handling Delay</t>
+  </si>
+  <si>
+    <t>181.2 ms</t>
+  </si>
+  <si>
+    <t>TC-292</t>
+  </si>
+  <si>
+    <t>Shared Family Settings Sync Offline Error Recovery</t>
+  </si>
+  <si>
+    <t>780.7 ms</t>
+  </si>
+  <si>
+    <t>TC-293</t>
+  </si>
+  <si>
+    <t>User Profile Form Field Constraints Validator Delay</t>
+  </si>
+  <si>
+    <t>65.2 ms</t>
+  </si>
+  <si>
+    <t>TC-294</t>
+  </si>
+  <si>
+    <t>SQLite Query Error Rollback Transaction Duration</t>
+  </si>
+  <si>
+    <t>83.5 ms</t>
+  </si>
+  <si>
+    <t>TC-295</t>
+  </si>
+  <si>
+    <t>Network Socket Timeout Event Handler Dispatch Time</t>
+  </si>
+  <si>
+    <t>78.5 ms</t>
+  </si>
+  <si>
+    <t>TC-296</t>
+  </si>
+  <si>
+    <t>App Background Recovery Notification Reschedule Delay</t>
+  </si>
+  <si>
+    <t>503.8 ms</t>
+  </si>
+  <si>
+    <t>TC-297</t>
+  </si>
+  <si>
+    <t>Low Battery Mode Alarm Schedulers Optimization Delay</t>
+  </si>
+  <si>
+    <t>243.6 ms</t>
+  </si>
+  <si>
+    <t>TC-298</t>
+  </si>
+  <si>
+    <t>Google Play Services Version Exception Notification Delay</t>
+  </si>
+  <si>
+    <t>393.1 ms</t>
+  </si>
+  <si>
+    <t>TC-299</t>
+  </si>
+  <si>
+    <t>Asset File Missing Fallback Resource Resolve Time</t>
+  </si>
+  <si>
+    <t>59.8 ms</t>
+  </si>
+  <si>
+    <t>TC-300</t>
+  </si>
+  <si>
+    <t>WebView Hardware Acceleration Exception Recovery Time</t>
+  </si>
+  <si>
+    <t>510.8 ms</t>
+  </si>
+  <si>
+    <t>TC-301</t>
+  </si>
+  <si>
+    <t>Sound Alert Player Output Exception Reset Latency</t>
+  </si>
+  <si>
+    <t>216.7 ms</t>
+  </si>
+  <si>
+    <t>TC-302</t>
+  </si>
+  <si>
+    <t>Biometric Hardware Sensor Lockout Release Backoff Delay</t>
+  </si>
+  <si>
+    <t>3274.3 ms</t>
+  </si>
+  <si>
+    <t>TC-303</t>
+  </si>
+  <si>
+    <t>WorkManager Worker Class Not Found Exception Handler Time</t>
+  </si>
+  <si>
+    <t>313.3 ms</t>
+  </si>
+  <si>
+    <t>TC-304</t>
+  </si>
+  <si>
+    <t>SharedPreferences Write Disk Exception Recovery Latency</t>
+  </si>
+  <si>
+    <t>151.1 ms</t>
+  </si>
+  <si>
+    <t>TC-305</t>
+  </si>
+  <si>
+    <t>System UI Frame Layout Measure Loop Safety Reset Time</t>
+  </si>
+  <si>
+    <t>91.1 ms</t>
   </si>
 </sst>
 </file>
@@ -2504,7 +3431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2559,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="5">
-        <v>200</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2567,7 +3494,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="6">
-        <v>200</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4614,10 +5541,10 @@
         <v>319</v>
       </c>
       <c r="D100" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E100" s="10" t="s">
         <v>320</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>321</v>
       </c>
       <c r="F100" s="10">
         <v>100</v>
@@ -4628,19 +5555,19 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C101" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D101" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="E101" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>325</v>
       </c>
       <c r="F101" s="10">
         <v>100</v>
@@ -4651,19 +5578,19 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C102" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D102" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="E102" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="F102" s="10">
         <v>100</v>
@@ -4674,19 +5601,19 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="E103" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>333</v>
       </c>
       <c r="F103" s="10">
         <v>100</v>
@@ -4697,19 +5624,19 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D104" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="E104" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="F104" s="10">
         <v>100</v>
@@ -4720,19 +5647,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C105" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="E105" s="10" t="s">
         <v>340</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>341</v>
       </c>
       <c r="F105" s="10">
         <v>100</v>
@@ -4743,19 +5670,19 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C106" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D106" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="E106" s="10" t="s">
         <v>344</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>345</v>
       </c>
       <c r="F106" s="10">
         <v>100</v>
@@ -4766,19 +5693,19 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C107" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D107" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="E107" s="10" t="s">
         <v>348</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="F107" s="10">
         <v>100</v>
@@ -4789,19 +5716,19 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C108" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D108" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="E108" s="10" t="s">
         <v>352</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>353</v>
       </c>
       <c r="F108" s="10">
         <v>100</v>
@@ -4812,19 +5739,19 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C109" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D109" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="E109" s="10" t="s">
         <v>356</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="F109" s="10">
         <v>100</v>
@@ -4835,19 +5762,19 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C110" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D110" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="E110" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>361</v>
       </c>
       <c r="F110" s="10">
         <v>100</v>
@@ -4858,16 +5785,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D111" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>271</v>
@@ -4881,19 +5808,19 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D112" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="E112" s="10" t="s">
         <v>367</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>368</v>
       </c>
       <c r="F112" s="10">
         <v>100</v>
@@ -4904,19 +5831,19 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C113" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D113" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="E113" s="10" t="s">
         <v>371</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>372</v>
       </c>
       <c r="F113" s="10">
         <v>100</v>
@@ -4927,19 +5854,19 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C114" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D114" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="E114" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>376</v>
       </c>
       <c r="F114" s="10">
         <v>100</v>
@@ -4950,19 +5877,19 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C115" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D115" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="E115" s="10" t="s">
         <v>379</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>380</v>
       </c>
       <c r="F115" s="10">
         <v>100</v>
@@ -4973,19 +5900,19 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C116" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D116" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="E116" s="10" t="s">
         <v>383</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>384</v>
       </c>
       <c r="F116" s="10">
         <v>100</v>
@@ -4996,19 +5923,19 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C117" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D117" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="E117" s="10" t="s">
         <v>387</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>388</v>
       </c>
       <c r="F117" s="10">
         <v>100</v>
@@ -5019,19 +5946,19 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>256</v>
       </c>
       <c r="C118" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="E118" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="F118" s="10">
         <v>100</v>
@@ -5042,19 +5969,19 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="C119" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="D119" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="E119" s="10" t="s">
         <v>396</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>397</v>
       </c>
       <c r="F119" s="10">
         <v>100</v>
@@ -5065,16 +5992,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C120" s="4" t="s">
+      <c r="D120" s="10" t="s">
         <v>399</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>400</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>31</v>
@@ -5088,16 +6015,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C121" s="4" t="s">
+      <c r="D121" s="10" t="s">
         <v>402</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>403</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>31</v>
@@ -5111,16 +6038,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B122" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C122" s="4" t="s">
+      <c r="D122" s="10" t="s">
         <v>405</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>406</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>173</v>
@@ -5134,16 +6061,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C123" s="4" t="s">
+      <c r="D123" s="10" t="s">
         <v>408</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>409</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>134</v>
@@ -5157,16 +6084,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C124" s="4" t="s">
+      <c r="D124" s="10" t="s">
         <v>411</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>412</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>31</v>
@@ -5180,16 +6107,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B125" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C125" s="4" t="s">
+      <c r="D125" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>415</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>31</v>
@@ -5203,16 +6130,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="B126" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="4" t="s">
+      <c r="D126" s="10" t="s">
         <v>417</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>418</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>31</v>
@@ -5226,16 +6153,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C127" s="4" t="s">
+      <c r="D127" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>31</v>
@@ -5249,16 +6176,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B128" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C128" s="4" t="s">
+      <c r="D128" s="10" t="s">
         <v>423</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>424</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>31</v>
@@ -5272,16 +6199,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B129" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C129" s="4" t="s">
+      <c r="D129" s="10" t="s">
         <v>426</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>427</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>31</v>
@@ -5295,16 +6222,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C130" s="4" t="s">
+      <c r="D130" s="10" t="s">
         <v>429</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>430</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>31</v>
@@ -5318,16 +6245,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C131" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C131" s="4" t="s">
+      <c r="D131" s="10" t="s">
         <v>432</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>433</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>31</v>
@@ -5341,16 +6268,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B132" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C132" s="4" t="s">
+      <c r="D132" s="10" t="s">
         <v>435</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>436</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>31</v>
@@ -5364,16 +6291,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B133" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C133" s="4" t="s">
+      <c r="D133" s="10" t="s">
         <v>438</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>439</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>31</v>
@@ -5387,16 +6314,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B134" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C134" s="4" t="s">
+      <c r="D134" s="10" t="s">
         <v>441</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>442</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>31</v>
@@ -5410,16 +6337,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C135" s="4" t="s">
+      <c r="D135" s="10" t="s">
         <v>444</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>445</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>31</v>
@@ -5433,16 +6360,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C136" s="4" t="s">
+      <c r="D136" s="10" t="s">
         <v>447</v>
-      </c>
-      <c r="D136" s="10" t="s">
-        <v>448</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>31</v>
@@ -5456,16 +6383,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C137" s="4" t="s">
+      <c r="D137" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="D137" s="10" t="s">
-        <v>451</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>31</v>
@@ -5479,16 +6406,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B138" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C138" s="4" t="s">
+      <c r="D138" s="10" t="s">
         <v>453</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>454</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>97</v>
@@ -5502,16 +6429,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C139" s="4" t="s">
+      <c r="D139" s="10" t="s">
         <v>456</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>457</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>166</v>
@@ -5525,16 +6452,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C140" s="4" t="s">
+      <c r="D140" s="10" t="s">
         <v>459</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>460</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>31</v>
@@ -5548,16 +6475,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B141" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C141" s="4" t="s">
+      <c r="D141" s="10" t="s">
         <v>462</v>
-      </c>
-      <c r="D141" s="10" t="s">
-        <v>463</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>39</v>
@@ -5571,16 +6498,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="B142" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C142" s="4" t="s">
+      <c r="D142" s="10" t="s">
         <v>465</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>466</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>173</v>
@@ -5594,16 +6521,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C143" s="4" t="s">
+      <c r="D143" s="10" t="s">
         <v>468</v>
-      </c>
-      <c r="D143" s="10" t="s">
-        <v>469</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>35</v>
@@ -5617,16 +6544,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="B144" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C144" s="4" t="s">
+      <c r="D144" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>472</v>
       </c>
       <c r="E144" s="10" t="s">
         <v>192</v>
@@ -5640,16 +6567,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="B145" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C145" s="4" t="s">
+      <c r="D145" s="10" t="s">
         <v>474</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>475</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>159</v>
@@ -5663,19 +6590,19 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="B146" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C146" s="4" t="s">
+      <c r="D146" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="E146" s="10" t="s">
         <v>478</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>479</v>
       </c>
       <c r="F146" s="10">
         <v>100</v>
@@ -5686,19 +6613,19 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="B147" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C147" s="4" t="s">
+      <c r="D147" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="E147" s="10" t="s">
         <v>482</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>483</v>
       </c>
       <c r="F147" s="10">
         <v>100</v>
@@ -5709,16 +6636,16 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C148" s="4" t="s">
+      <c r="D148" s="10" t="s">
         <v>485</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>486</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>31</v>
@@ -5732,16 +6659,16 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B149" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C149" s="4" t="s">
+      <c r="D149" s="10" t="s">
         <v>488</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>489</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>173</v>
@@ -5755,16 +6682,16 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B150" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C150" s="4" t="s">
+      <c r="D150" s="10" t="s">
         <v>491</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>492</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>31</v>
@@ -5778,16 +6705,16 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>494</v>
-      </c>
       <c r="D151" s="10" t="s">
-        <v>495</v>
+        <v>225</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>199</v>
@@ -5801,19 +6728,19 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D152" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C152" s="4" t="s">
+      <c r="E152" s="10" t="s">
         <v>497</v>
-      </c>
-      <c r="D152" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>499</v>
       </c>
       <c r="F152" s="10">
         <v>100</v>
@@ -5824,16 +6751,16 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D153" s="10" t="s">
         <v>500</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>502</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>35</v>
@@ -5847,16 +6774,16 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="D154" s="10" t="s">
         <v>504</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="D154" s="10" t="s">
-        <v>506</v>
       </c>
       <c r="E154" s="10" t="s">
         <v>293</v>
@@ -5870,13 +6797,13 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>27</v>
@@ -5893,13 +6820,13 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>27</v>
@@ -5916,13 +6843,13 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>27</v>
@@ -5939,13 +6866,13 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="10" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>27</v>
@@ -5962,13 +6889,13 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D159" s="10" t="s">
         <v>27</v>
@@ -5985,13 +6912,13 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D160" s="10" t="s">
         <v>27</v>
@@ -6008,13 +6935,13 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="10" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D161" s="10" t="s">
         <v>27</v>
@@ -6031,13 +6958,13 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D162" s="10" t="s">
         <v>27</v>
@@ -6054,13 +6981,13 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>27</v>
@@ -6077,13 +7004,13 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D164" s="10" t="s">
         <v>27</v>
@@ -6100,13 +7027,13 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="10" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D165" s="10" t="s">
         <v>27</v>
@@ -6123,13 +7050,13 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="10" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D166" s="10" t="s">
         <v>27</v>
@@ -6146,13 +7073,13 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D167" s="10" t="s">
         <v>27</v>
@@ -6169,13 +7096,13 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D168" s="10" t="s">
         <v>27</v>
@@ -6192,13 +7119,13 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="10" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>27</v>
@@ -6215,13 +7142,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D170" s="10" t="s">
         <v>27</v>
@@ -6238,13 +7165,13 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>27</v>
@@ -6261,13 +7188,13 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>27</v>
@@ -6284,19 +7211,19 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D173" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="B173" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="C173" s="4" t="s">
+      <c r="E173" s="10" t="s">
         <v>544</v>
-      </c>
-      <c r="D173" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="E173" s="10" t="s">
-        <v>546</v>
       </c>
       <c r="F173" s="10">
         <v>100</v>
@@ -6307,19 +7234,19 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D174" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="B174" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="C174" s="4" t="s">
+      <c r="E174" s="10" t="s">
         <v>548</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="E174" s="10" t="s">
-        <v>550</v>
       </c>
       <c r="F174" s="10">
         <v>100</v>
@@ -6330,13 +7257,13 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D175" s="10" t="s">
         <v>27</v>
@@ -6353,13 +7280,13 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="10" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>27</v>
@@ -6376,13 +7303,13 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="10" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>27</v>
@@ -6399,13 +7326,13 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D178" s="10" t="s">
         <v>27</v>
@@ -6422,13 +7349,13 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D179" s="10" t="s">
         <v>27</v>
@@ -6445,19 +7372,19 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D180" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="B180" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="C180" s="4" t="s">
+      <c r="E180" s="10" t="s">
         <v>562</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="E180" s="10" t="s">
-        <v>564</v>
       </c>
       <c r="F180" s="10">
         <v>100</v>
@@ -6468,13 +7395,13 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="10" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D181" s="10" t="s">
         <v>27</v>
@@ -6491,13 +7418,13 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="10" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D182" s="10" t="s">
         <v>27</v>
@@ -6514,13 +7441,13 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="10" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>27</v>
@@ -6537,16 +7464,16 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="D184" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D184" s="10" t="s">
-        <v>574</v>
       </c>
       <c r="E184" s="10" t="s">
         <v>289</v>
@@ -6560,16 +7487,16 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D185" s="10" t="s">
         <v>575</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="D185" s="10" t="s">
-        <v>577</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>293</v>
@@ -6583,19 +7510,19 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D186" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="B186" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C186" s="4" t="s">
+      <c r="E186" s="10" t="s">
         <v>579</v>
-      </c>
-      <c r="D186" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="E186" s="10" t="s">
-        <v>581</v>
       </c>
       <c r="F186" s="10">
         <v>100</v>
@@ -6606,13 +7533,13 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="10" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>133</v>
@@ -6629,19 +7556,19 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="D188" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="B188" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C188" s="4" t="s">
+      <c r="E188" s="10" t="s">
         <v>585</v>
-      </c>
-      <c r="D188" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="E188" s="10" t="s">
-        <v>587</v>
       </c>
       <c r="F188" s="10">
         <v>100</v>
@@ -6652,16 +7579,16 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="10" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>457</v>
+        <v>228</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>192</v>
@@ -6675,13 +7602,13 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>150</v>
@@ -6698,19 +7625,19 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D191" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="B191" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C191" s="4" t="s">
+      <c r="E191" s="10" t="s">
         <v>593</v>
-      </c>
-      <c r="D191" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="E191" s="10" t="s">
-        <v>595</v>
       </c>
       <c r="F191" s="10">
         <v>100</v>
@@ -6721,13 +7648,13 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="10" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>27</v>
@@ -6744,13 +7671,13 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="10" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>27</v>
@@ -6767,16 +7694,16 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="D194" s="10" t="s">
         <v>600</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="D194" s="10" t="s">
-        <v>602</v>
       </c>
       <c r="E194" s="10" t="s">
         <v>159</v>
@@ -6790,13 +7717,13 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="10" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>27</v>
@@ -6813,19 +7740,19 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="D196" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="B196" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C196" s="4" t="s">
+      <c r="E196" s="10" t="s">
         <v>606</v>
-      </c>
-      <c r="D196" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="E196" s="10" t="s">
-        <v>608</v>
       </c>
       <c r="F196" s="10">
         <v>100</v>
@@ -6836,13 +7763,13 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="10" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>27</v>
@@ -6859,13 +7786,13 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="10" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>27</v>
@@ -6882,19 +7809,19 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="D199" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="B199" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C199" s="4" t="s">
+      <c r="E199" s="10" t="s">
         <v>614</v>
-      </c>
-      <c r="D199" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="E199" s="10" t="s">
-        <v>616</v>
       </c>
       <c r="F199" s="10">
         <v>100</v>
@@ -6905,19 +7832,19 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="D200" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="B200" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C200" s="4" t="s">
+      <c r="E200" s="10" t="s">
         <v>618</v>
-      </c>
-      <c r="D200" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="E200" s="10" t="s">
-        <v>620</v>
       </c>
       <c r="F200" s="10">
         <v>100</v>
@@ -6928,19 +7855,19 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D201" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="B201" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C201" s="4" t="s">
+      <c r="E201" s="10" t="s">
         <v>622</v>
-      </c>
-      <c r="D201" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="E201" s="10" t="s">
-        <v>624</v>
       </c>
       <c r="F201" s="10">
         <v>100</v>
@@ -6951,19 +7878,19 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D202" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="B202" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C202" s="4" t="s">
+      <c r="E202" s="10" t="s">
         <v>626</v>
-      </c>
-      <c r="D202" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="E202" s="10" t="s">
-        <v>628</v>
       </c>
       <c r="F202" s="10">
         <v>100</v>
@@ -6974,16 +7901,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="D203" s="10" t="s">
         <v>629</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="D203" s="10" t="s">
-        <v>631</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>229</v>
@@ -6997,19 +7924,19 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D204" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="B204" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C204" s="4" t="s">
+      <c r="E204" s="10" t="s">
         <v>633</v>
-      </c>
-      <c r="D204" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="E204" s="10" t="s">
-        <v>635</v>
       </c>
       <c r="F204" s="10">
         <v>100</v>
@@ -7020,19 +7947,19 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="D205" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="B205" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C205" s="4" t="s">
+      <c r="E205" s="10" t="s">
         <v>637</v>
-      </c>
-      <c r="D205" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="E205" s="10" t="s">
-        <v>639</v>
       </c>
       <c r="F205" s="10">
         <v>100</v>
@@ -7043,16 +7970,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D206" s="10" t="s">
         <v>640</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="D206" s="10" t="s">
-        <v>642</v>
       </c>
       <c r="E206" s="10" t="s">
         <v>251</v>
@@ -7066,19 +7993,19 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D207" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="B207" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C207" s="4" t="s">
+      <c r="E207" s="10" t="s">
         <v>644</v>
-      </c>
-      <c r="D207" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="E207" s="10" t="s">
-        <v>646</v>
       </c>
       <c r="F207" s="10">
         <v>100</v>
@@ -7089,13 +8016,13 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="10" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>27</v>
@@ -7112,19 +8039,19 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D209" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="B209" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C209" s="4" t="s">
+      <c r="E209" s="10" t="s">
         <v>650</v>
-      </c>
-      <c r="D209" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="E209" s="10" t="s">
-        <v>652</v>
       </c>
       <c r="F209" s="10">
         <v>100</v>
@@ -7135,19 +8062,19 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="D210" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="B210" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C210" s="4" t="s">
+      <c r="E210" s="10" t="s">
         <v>654</v>
-      </c>
-      <c r="D210" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="E210" s="10" t="s">
-        <v>656</v>
       </c>
       <c r="F210" s="10">
         <v>100</v>
@@ -7158,19 +8085,19 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D211" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B211" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C211" s="4" t="s">
+      <c r="E211" s="10" t="s">
         <v>658</v>
-      </c>
-      <c r="D211" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="E211" s="10" t="s">
-        <v>660</v>
       </c>
       <c r="F211" s="10">
         <v>100</v>
@@ -7181,19 +8108,19 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D212" s="10" t="s">
         <v>661</v>
       </c>
-      <c r="B212" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C212" s="4" t="s">
+      <c r="E212" s="10" t="s">
         <v>662</v>
-      </c>
-      <c r="D212" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="E212" s="10" t="s">
-        <v>664</v>
       </c>
       <c r="F212" s="10">
         <v>100</v>
@@ -7204,24 +8131,2439 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="D213" s="10" t="s">
         <v>665</v>
       </c>
-      <c r="B213" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C213" s="4" t="s">
+      <c r="E213" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="F213" s="10">
+        <v>100</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="E213" s="10" t="s">
+      <c r="B214" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="F213" s="10">
-        <v>100</v>
-      </c>
-      <c r="G213" s="8" t="s">
+      <c r="C214" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="E214" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F214" s="10">
+        <v>100</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F215" s="10">
+        <v>100</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F216" s="10">
+        <v>100</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="F217" s="10">
+        <v>100</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F218" s="10">
+        <v>100</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F219" s="10">
+        <v>100</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F220" s="10">
+        <v>100</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F221" s="10">
+        <v>100</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F222" s="10">
+        <v>100</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="E223" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F223" s="10">
+        <v>100</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F224" s="10">
+        <v>100</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D225" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="E225" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F225" s="10">
+        <v>100</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F226" s="10">
+        <v>100</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F227" s="10">
+        <v>100</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F228" s="10">
+        <v>100</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="D229" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="E229" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F229" s="10">
+        <v>100</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="D230" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F230" s="10">
+        <v>100</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D231" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F231" s="10">
+        <v>100</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="D232" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="E232" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F232" s="10">
+        <v>100</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F233" s="10">
+        <v>100</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D234" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E234" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F234" s="10">
+        <v>100</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D235" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E235" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F235" s="10">
+        <v>100</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E236" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F236" s="10">
+        <v>100</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E237" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F237" s="10">
+        <v>100</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E238" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F238" s="10">
+        <v>100</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="E239" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F239" s="10">
+        <v>100</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="D240" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="F240" s="10">
+        <v>100</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D241" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="E241" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="F241" s="10">
+        <v>100</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="F242" s="10">
+        <v>100</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="D243" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="E243" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F243" s="10">
+        <v>100</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="E244" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="F244" s="10">
+        <v>100</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="E245" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="F245" s="10">
+        <v>100</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F246" s="10">
+        <v>100</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="E247" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="F247" s="10">
+        <v>100</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F248" s="10">
+        <v>100</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="E249" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="F249" s="10">
+        <v>100</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F250" s="10">
+        <v>100</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F251" s="10">
+        <v>100</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F252" s="10">
+        <v>100</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F253" s="10">
+        <v>100</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F254" s="10">
+        <v>100</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F255" s="10">
+        <v>100</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>795</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F256" s="10">
+        <v>100</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F257" s="10">
+        <v>100</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="F258" s="10">
+        <v>100</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="D259" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F259" s="10">
+        <v>100</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F260" s="10">
+        <v>100</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="D261" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="E261" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F261" s="10">
+        <v>100</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="D262" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="E262" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F262" s="10">
+        <v>100</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F263" s="10">
+        <v>100</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="D264" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F264" s="10">
+        <v>100</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D265" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E265" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F265" s="10">
+        <v>100</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="10" t="s">
+        <v>821</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="D266" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F266" s="10">
+        <v>100</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D267" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E267" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F267" s="10">
+        <v>100</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="D268" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F268" s="10">
+        <v>100</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="D269" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="E269" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="F269" s="10">
+        <v>100</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D270" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="E270" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="F270" s="10">
+        <v>100</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="D271" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="E271" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="F271" s="10">
+        <v>100</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="D272" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="E272" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="F272" s="10">
+        <v>100</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="D273" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="E273" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F273" s="10">
+        <v>100</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="D274" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="E274" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F274" s="10">
+        <v>100</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D275" s="10" t="s">
+        <v>851</v>
+      </c>
+      <c r="E275" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F275" s="10">
+        <v>100</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="D276" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="E276" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F276" s="10">
+        <v>100</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="D277" s="10" t="s">
+        <v>857</v>
+      </c>
+      <c r="E277" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F277" s="10">
+        <v>100</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D278" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="E278" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F278" s="10">
+        <v>100</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="D279" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="E279" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F279" s="10">
+        <v>100</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D280" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="E280" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="F280" s="10">
+        <v>100</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="E281" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F281" s="10">
+        <v>100</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="D282" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="E282" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="F282" s="10">
+        <v>100</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D283" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="E283" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F283" s="10">
+        <v>100</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E284" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F284" s="10">
+        <v>100</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="D285" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E285" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F285" s="10">
+        <v>100</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="10" t="s">
+        <v>883</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="D286" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E286" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F286" s="10">
+        <v>100</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="10" t="s">
+        <v>885</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E287" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F287" s="10">
+        <v>100</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="D288" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E288" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F288" s="10">
+        <v>100</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="D289" s="10" t="s">
+        <v>891</v>
+      </c>
+      <c r="E289" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F289" s="10">
+        <v>100</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="E290" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F290" s="10">
+        <v>100</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="D291" s="10" t="s">
+        <v>897</v>
+      </c>
+      <c r="E291" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="F291" s="10">
+        <v>100</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="E292" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F292" s="10">
+        <v>100</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>903</v>
+      </c>
+      <c r="E293" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F293" s="10">
+        <v>100</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="E294" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F294" s="10">
+        <v>100</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="D295" s="10" t="s">
+        <v>909</v>
+      </c>
+      <c r="E295" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F295" s="10">
+        <v>100</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D296" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="E296" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F296" s="10">
+        <v>100</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="D297" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="E297" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F297" s="10">
+        <v>100</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>918</v>
+      </c>
+      <c r="E298" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F298" s="10">
+        <v>100</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="D299" s="10" t="s">
+        <v>921</v>
+      </c>
+      <c r="E299" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F299" s="10">
+        <v>100</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="D300" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="E300" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F300" s="10">
+        <v>100</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D301" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="E301" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F301" s="10">
+        <v>100</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="D302" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="E302" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F302" s="10">
+        <v>100</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E303" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F303" s="10">
+        <v>100</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="E304" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F304" s="10">
+        <v>100</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="E305" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F305" s="10">
+        <v>100</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="E306" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F306" s="10">
+        <v>100</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="D307" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="E307" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F307" s="10">
+        <v>100</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="E308" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F308" s="10">
+        <v>100</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="E309" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F309" s="10">
+        <v>100</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="E310" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F310" s="10">
+        <v>100</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="E311" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F311" s="10">
+        <v>100</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="E312" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F312" s="10">
+        <v>100</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="E313" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F313" s="10">
+        <v>100</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="D314" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="E314" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F314" s="10">
+        <v>100</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="E315" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F315" s="10">
+        <v>100</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="D316" s="10" t="s">
+        <v>971</v>
+      </c>
+      <c r="E316" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F316" s="10">
+        <v>100</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="D317" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="E317" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F317" s="10">
+        <v>100</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="D318" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="E318" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F318" s="10">
+        <v>100</v>
+      </c>
+      <c r="G318" s="8" t="s">
         <v>27</v>
       </c>
     </row>
